--- a/untitled folder/HSC_Physics_2nd_Paper_Chapter_02_Static_Electricity.xlsx
+++ b/untitled folder/HSC_Physics_2nd_Paper_Chapter_02_Static_Electricity.xlsx
@@ -1168,11 +1168,6 @@
           <t>কুলম্বের সূত্রের ভেক্টর রূপ $\vec{F}_{12} = \frac{1}{4\pi\varepsilon_0}\frac{q_1 q_2}{|\vec{r}_1 - \vec{r}_2|^3}(\vec{r}_1 - \vec{r}_2)$ প্রতিপাদন করো। আর্নশ-এর উপপাদ্য (Earnshaw's Theorem) বিবৃত করো এবং দেখাও যে কেন কেবলমাত্র স্থিরবৈদ্যুতিক কুলম্ব বলের উপস্থিতিতে কোনো বিন্দু আধানের সমষ্টি কোনো অবস্থাতেই একটি স্থায়ী স্থিতিশীল সাম্যাবস্থায় (stable electrostatic equilibrium) থাকতে পারে না।</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>কুলম্বের ভেক্টর রূপ ও আর্নশ উপপাদ্যের প্রমাণ:</t>
@@ -1218,11 +1213,6 @@
           <t>$L$ দৈর্ঘ্যের দুটি অপরিবাহী হালকা সুতো দ্বারা একটি সাধারণ বিন্দু থেকে ঝুলানো দুটি অভিন্ন ছোট পিথ বলের প্রতিটির ভর $m$ এবং প্রতিটিতে আধান $q$ প্রদান করা হলো। বল দুটি পারস্পরিক বিকর্ষণের কারণে সাম্যাবস্থায় $x$ দূরত্বে অবস্থান করে ($x \ll L$)। প্রমাণ করো যে সাম্য দূরত্ব $x = \left(\frac{q^2 L}{2\pi\varepsilon_0 m g}\right)^{1/3}$। যদি উভয় বল থেকে আধান ধ্রুব হারে লিক হয়ে বাতাসে অপসৃত হতে থাকে ($dq/dt = \text{const}$), তবে বল দুটির পরস্পরের দিকে এগিয়ে আসার বেগ দূরত্বের সাথে কীভাবে পরিবর্তিত হয় ($v \propto x^{-1/2}$) তা প্রতিপাদন করো।</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>ঝুলন্ত আধানের সাম্য দূরত্ব ও আধান ক্ষরণে আপেক্ষিক বেগ:</t>
@@ -1268,11 +1258,6 @@
           <t>$R$ ব্যাসার্ধের একটি পাতলা বৃত্তাকার রিংয়ে সুষমভাবে মোট ধনাত্মক আধান $Q$ বণ্টিত আছে। রিংয়ের অক্ষের ওপর কেন্দ্র থেকে $x$ দূরত্বে তড়িৎ ক্ষেত্র প্রাবল্যের রাশিমালা $E(x) = \frac{1}{4\pi\varepsilon_0}\frac{Q x}{(x^2 + R^2)^{3/2}}$ প্রতিপাদন করো। অক্ষের ওপর কোন অবস্থানে তড়িৎ ক্ষেত্র সর্বাধিক হয় এবং সেই সর্বাধিক তড়িৎ ক্ষেত্রের মান কত?</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>আহিত রিংয়ের অক্ষীয় তড়িৎ ক্ষেত্র ও চরমমান প্রতিপাদন:</t>
@@ -1318,11 +1303,6 @@
           <t>$L$ দৈর্ঘ্যের একটি সরু সোজা রডে সুষম রৈখিক আধান ঘনত্ব $\lambda$ বিদ্যমান। রডের লম্ব-দ্বিখণ্ডকের ওপর রড থেকে $r$ লম্ব দূরত্বে তড়িৎ ক্ষেত্র প্রাবল্যের রাশিমালা প্রতিপাদন করো। রডটির দৈর্ঘ্য অসীম ($L \to \infty$) হলে ফলাফলটি কীভাবে অসীম তারের বিখ্যাত সূত্রে ($E = \frac{\lambda}{2\pi\varepsilon_0 r}$) রূপান্তরিত হয় দেখাও।</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>সসীম ও অসীম আহিত রডের লম্ব-দ্বিখণ্ডকে তড়িৎ ক্ষেত্র প্রতিপাদন:</t>
@@ -1368,11 +1348,6 @@
           <t>দুটি সমান ধনাত্মক আধান $+q$ পরস্পর $2d$ দূরত্বে $(\pm d, 0)$ অবস্থানে দৃঢ়ভাবে আটকানো আছে। তাদের সংযোগকারী রেখার মধ্যবিন্দুতে একটি তৃতীয় আধান $-Q$ ($m$ ভর বিশিষ্ট) রাখা হলো। কণাটিকে (ক) সংযোগকারী রেখা ($x$-অক্ষ) বরাবর এবং (খ) লম্ব-দ্বিখণ্ডক ($y$-অক্ষ) বরাবর সামান্য স্থানান্তরিত করলে কোন ক্ষেত্রে গতিটি সরল ছন্দিত স্পন্দন হবে? সেই স্পন্দনের পর্যায়কাল নির্ণয় করো।</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>দ্বি-আধান ব্যবস্থায় অক্ষীয় ও লম্বীয় গতিশীলতার স্থিতিশীলতা:</t>
@@ -1418,11 +1393,6 @@
           <t>$R$ ব্যাসার্ধের একটি সুষম বৃত্তাকার পাতলা ডিস্কে পৃষ্ঠ আধান ঘনত্ব $\sigma$ বিদ্যমান। ডিস্কের অক্ষের ওপর কেন্দ্র থেকে $x$ দূরত্বে তড়িৎ ক্ষেত্র প্রাবল্য $E(x) = \frac{\sigma}{2\varepsilon_0}\left(1 - \frac{x}{\sqrt{x^2 + R^2}}\right)$ প্রতিপাদন করো। ডিস্কের ব্যাসার্ধ অসীম ($R \to \infty$) হলে এবং দূরবর্তী বিন্দুতে ($x \gg R$) তড়িৎ ক্ষেত্রের আচরণ বিশ্লেষণ করো।</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>আহিত ডিস্কের অক্ষীয় তড়িৎ ক্ষেত্র ও সীমামান বিশ্লেষণ:</t>
@@ -1468,11 +1438,6 @@
           <t>$R$ ব্যাসার্ধের একটি অর্ধ-বৃত্তাকার সরু তারে সুষম রৈখিক আধান ঘনত্ব $\lambda$ রয়েছে। তারটির বক্রতার কেন্দ্রে লব্ধি তড়িৎ ক্ষেত্র প্রাবল্য $E = \frac{\lambda}{2\pi\varepsilon_0 R}$ প্রতিপাদন করো। যদি অর্ধ-বৃত্তের এক চতুর্থাংশে $+\lambda$ এবং অপর চতুর্থাংশে $-\lambda$ আধান থাকে, তবে কেন্দ্রে তড়িৎ ক্ষেত্রের মান ও অভিমুখ কী হবে?</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>অর্ধ-বৃত্তাকার আহিত তারের কেন্দ্রবিন্দুতে তড়িৎ ক্ষেত্র:</t>
@@ -1569,11 +1534,6 @@
           <t>দুটি ধনাত্মক আধান $+q$ এবং $+4q$ পরস্পর $L$ দূরত্বে অবস্থিত। তাদের সংযোগকারী রেখার ওপর একটি তৃতীয় আধান $Q$ কোথায় এবং কী মানে স্থাপন করলে সমগ্র ব্যবস্থাটি একটি পূর্ণ সাম্যাবস্থায় (all three charges in equilibrium) থাকবে? এই সাম্যাবস্থাটি কি স্থিতিশীল নাকি অস্থিতিশীল?</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>তিন আধান ব্যবস্থার সামগ্রিক সাম্যাবস্থা ও অস্থিতিশীলতা প্রমাণ:</t>
@@ -1619,11 +1579,6 @@
           <t>আইরোদভের সমস্যা: $R$ ব্যাসার্ধের একটি গোলকীয় মেঘের আয়তন আধান ঘনত্ব সুষম নয় এবং তা কেন্দ্র থেকে দূরত্বের সাথে $\rho(r) = \rho_0 \left(1 - \frac{r}{R}\right)$ সমীকরণ অনুসারে পরিবর্তিত হয়। গোলকটির কেন্দ্র থেকে $r &lt; R$ এবং $r &gt; R$ দূরত্বের বিন্দুতে তড়িৎ ক্ষেত্র প্রাবল্য $E(r)$-এর রাশিমালা নির্ণয় করো। কেন্দ্র থেকে কত দূরত্বে তড়িৎ ক্ষেত্র সর্বাধিক হবে?</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>অসুষম আধান ঘনত্বের গোলকের তড়িৎ ক্ষেত্র ও চরমমান নির্ণয়:</t>
@@ -1669,11 +1624,6 @@
           <t>তড়িৎ ফ্লাক্সের সংজ্ঞা দাও এবং গাউসের সূত্র $\oint \vec{E}\cdot d\vec{A} = \frac{Q_{\text{enclosed}}}{\varepsilon_0}$ সমাকলন ও ব্যবকলনীয় ($\nabla \cdot \vec{E} = \frac{\rho}{\varepsilon_0}$) উভয় রূপে উপস্থাপন করো। একটি গোলকীয় গাউসীয় তলের ক্ষেত্রফল দ্বিগুণ করলে তলটি দিয়ে অতিক্রান্ত মোট ফ্লাক্সের কোনো পরিবর্তন হবে কি?</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>গাউসের সূত্রের সমাকলন ও ব্যবকলনীয় রূপের বিশ্লেষণ:</t>
@@ -1719,11 +1669,6 @@
           <t>ঘন কোণ (Solid Angle $\Omega$) পদ্ধতি ব্যবহার করে প্রমাণ করো যে একটি বিন্দু আধান $q$ থেকে $d$ দূরত্বে অবস্থিত $R$ ব্যাসার্ধের একটি সমতল বৃত্তাকার ডিস্কের মধ্য দিয়ে অতিক্রান্ত মোট তড়িৎ ফ্লাক্স $\Phi_E = \frac{q}{2\varepsilon_0}\left(1 - \frac{d}{\sqrt{d^2 + R^2}}\right) = \frac{q}{2\varepsilon_0}(1 - \cos\alpha)$, যেখানে $\alpha$ হলো ডিস্কের পরিধি দ্বারা আধানে উৎপন্ন অর্ধ-শীর্ষ কোণ।</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>ঘন কোণ পদ্ধতিতে ডিস্কের ফ্লাক্স প্রতিপাদন:</t>
@@ -1769,11 +1714,6 @@
           <t>একটি $a$ বাহু বিশিষ্ট সুষম ঘনকের: (i) একটি শীর্ষবিন্দুতে (corner), (ii) একটি ধারের মধ্যবিন্দুতে (edge center), এবং (iii) একটি তলের কেন্দ্রে (face center) একটি বিন্দু আধান $q$ স্থাপিত হলে ঘনকটির ভেতর দিয়ে অতিক্রান্ত মোট ফ্লাক্স কত হবে?</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>ঘনকের বিভিন্ন অবস্থানে আধানের গাউসীয় প্রতিসাম্য ফ্লাক্স:</t>
@@ -1819,11 +1759,6 @@
           <t>গাউসের সূত্র প্রয়োগ করে প্রমাণ করো যে একটি সুষমভাবে আহিত গোলকীয় খোলসের (spherical shell) অভ্যন্তরে যেকোনো বিন্দুতে তড়িৎ ক্ষেত্র প্রাবল্য নিখুঁত শূন্য ($E_{\text{inside}} = 0$) এবং বাইরে এটি এমন আচরণ করে যেন সমস্ত আধান কেন্দ্রে কেন্দ্রীভূত ($E_{\text{outside}} = \frac{Q}{4\pi\varepsilon_0 r^2}$)। খোলসের উপরিভাগে তড়িৎ ক্ষেত্রের বিচ্ছিন্নতা (discontinuity) ব্যাখ্যা করো।</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>গোলকীয় খোলসে গাউসের সূত্র ও ক্ষেত্রের লাফানো বিচ্ছিন্নতা:</t>
@@ -1869,11 +1804,6 @@
           <t>আইরোদভের বিখ্যাত ক্যাভিটি সমস্যা: সুষম আয়তন আধান ঘনত্ব $\rho$ বিশিষ্ট একটি নিরেট গোলকের অভ্যন্তরে কেন্দ্র থেকে $\vec{a}$ দূরত্বে একটি ফাঁপা গোলকীয় গহ্বর (spherical cavity) তৈরি করা হলো। প্রমাণ করো যে গহ্বরের অভ্যন্তরে সর্বত্র তড়িৎ ক্ষেত্র সম্পূর্ণ সুষম এবং তার মান ও দিক $\vec{E} = \frac{\rho \vec{a}}{3\varepsilon_0}$ দ্বারা নির্ধারিত।</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>গোলকীয় ক্যাভিটিতে সুষম তড়িৎ ক্ষেত্র প্রতিপাদন:</t>
@@ -1919,11 +1849,6 @@
           <t>$R$ ব্যাসার্ধের একটি অসীম দীর্ঘ নিরেট সিলিন্ডারে সুষম আয়তন আধান ঘনত্ব $\rho$ বিদ্যমান। গাউসের সূত্র প্রয়োগ করে সিলিন্ডারের অক্ষ থেকে $r &lt; R$ এবং $r &gt; R$ দূরত্বের বিন্দুতে তড়িৎ ক্ষেত্র প্রাবল্য নির্ণয় করো।</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>আহিত অসীম সিলিন্ডারে গাউসের সূত্র প্রয়োগ:</t>
@@ -1969,11 +1894,6 @@
           <t>সুষম আয়তন আধান ঘনত্ব $\rho$ বিশিষ্ট একটি অসীম সমতল স্ল্যাবের (infinite slab) পুরুত্ব $2d$ (অর্থাৎ $-d \le x \le +d$)। স্ল্যাবের মধ্যতল ($x = 0$) থেকে $x$ দূরত্বে তড়িৎ ক্ষেত্র প্রাবল্যের সমীকরণ প্রতিপাদন করো (স্ল্যাবের অভ্যন্তরে এবং বাইরে উভয় ক্ষেত্রে)।</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>আহিত অসীম সমতল স্ল্যাবের তড়িৎ ক্ষেত্র প্রতিপাদন:</t>
@@ -2019,11 +1939,6 @@
           <t>পয়সনের সমীকরণ (Poisson's Equation) $\nabla^2 V = -\frac{\rho}{\varepsilon_0}$ এবং ল্যাপলাসের সমীকরণ (Laplace's Equation) $\nabla^2 V = 0$ প্রতিপাদন করো। স্থিরতড়িৎ বিজ্ঞানে কেন এই সমীকরণ দুটি বাউন্ডারি ভ্যালু সমস্যার একমাত্রিক সমাধান (Uniqueness Theorem) নিশ্চিত করে?</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>পয়সন ও ল্যাপলাস সমীকরণ এবং অনন্যতা উপপাদ্য:</t>
@@ -2069,11 +1984,6 @@
           <t>একটি অসীম সমতল সুষম আহিত তলে (পৃষ্ঠ আধান ঘনত্ব $\sigma$) $R$ ব্যাসার্ধের একটি বৃত্তাকার গর্ত (hole) করা হলো। গর্তের অক্ষের ওপর কেন্দ্র থেকে $x$ দূরত্বে তড়িৎ ক্ষেত্র প্রাবল্যের মান কত হবে? গর্তের ঠিক কেন্দ্রে ($x = 0$) তড়িৎ ক্ষেত্র কত?</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>আহিত সমতলে বৃত্তাকার গর্তের অক্ষীয় তড়িৎ ক্ষেত্র:</t>
@@ -2119,11 +2029,6 @@
           <t>একটি গোলকীয় অঞ্চলে আধান ঘনত্ব কেবল ব্যাসার্ধের ওপর নির্ভর করে এবং তা $\rho(r) = \frac{k}{r^2}$ ($r_1 \le r \le r_2$) সমীকরণ মেনে চলে। গাউসের সূত্র প্রয়োগ করে এই অঞ্চলে তড়িৎ ক্ষেত্র প্রাবল্য $E(r)$-এর রাশিমালা নির্ণয় করো। কেন এই ক্ষেত্রটি দূরত্বের ওপর সম্পূর্ণ নিরপেক্ষ ধ্রুবক হয়?</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>ব্যস্তবর্গীয় আধান ঘনত্বের ধ্রুবক তড়িৎ ক্ষেত্র প্রতিপাদন:</t>
@@ -2169,11 +2074,6 @@
           <t>তড়িৎ বিভবের সংজ্ঞা লাইন ইন্টিগ্রালের মাধ্যমে $V(\vec{r}) = -\int_\infty^{\vec{r}} \vec{E}\cdot d\vec{l}$ উপস্থাপন করো। প্রমাণ করো যে তড়িৎ ক্ষেত্র হলো বিভবের ঋণাত্মক গ্র্যাডিয়েন্ট ($\vec{E} = -\nabla V$)। একটি অঞ্চলে বিভব $V(x, y, z) = 6x - 8x y - 8y + 6y z$ হলে বিন্দু $(1, 1, 1)$-তে তড়িৎ ক্ষেত্র ভেক্টর $\vec{E}$ এবং তার পরম মান নির্ণয় করো।</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>বিভব গ্র্যাডিয়েন্ট ও তড়িৎ ক্ষেত্র ভেক্টর গণনা:</t>
@@ -2219,11 +2119,6 @@
           <t>সমবিভব তল (Equipotential Surface) বলতে কী বোঝায়? প্রমাণ করো যে: (i) সমবিভব তলের ওপর যেকোনো দুটি বিন্দুর মধ্যে কোনো আধান স্থানান্তরে কৃতকাজ নিখুঁত শূন্য, এবং (ii) তড়িৎ ক্ষেত্র রেখাগুলি সমবিভব তলের সাথে সর্বদা লম্বভাবে অবস্থান করে।</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>সমবিভব তলের বৈশিষ্ট্য ও লম্বতার প্রমাণ:</t>
@@ -2269,11 +2164,6 @@
           <t>$R$ ব্যাসার্ধের একটি সুষম আহিত গোলকীয় খোলসের (মোট আধান $Q$) জন্য কেন্দ্র থেকে $r &lt; R$ এবং $r \ge R$ দূরত্বের বিন্দুতে তড়িৎ বিভব $V(r)$-এর রাশিমালা নির্ণয় করো। খোলসের অভ্যন্তরে কেন্দ্রে বিভব পৃষ্ঠের বিভবের সমান ($V_{\text{center}} = V_{\text{surface}}$) হওয়ার কারণ ব্যাখ্যা করো।</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>গোলকীয় খোলসের তড়িৎ বিভব প্রোফাইল প্রতিপাদন:</t>
@@ -2319,11 +2209,6 @@
           <t>সুষম আয়তন আধান ঘনত্ব $\rho$ বিশিষ্ট $R$ ব্যাসার্ধের একটি নিরেট অপরিবাহী গোলকের মোট আধান $Q$। প্রমাণ করো যে গোলকের অভ্যন্তরে কেন্দ্র থেকে $r \le R$ দূরত্বে বিভব $V(r) = \frac{Q}{8\pi\varepsilon_0 R}\left(3 - \frac{r^2}{R^2}\right)$। দেখাও যে কেন্দ্রের বিভব পৃষ্ঠের বিভবের দেড় গুণ ($V_{\text{center}} = 1.5 V_{\text{surface}}$)।</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I25" t="inlineStr">
         <is>
           <t>নিরেট আহিত গোলকের অভ্যন্তরীণ বিভব প্রতিপাদন:</t>
@@ -2420,11 +2305,6 @@
           <t>$R$ ব্যাসার্ধের একটি সুষম আহিত নিরেট গোলকের (মোট আধান $Q$) স্থিরবৈদ্যুতিক স্ব-শক্তি $U = \frac{3Q^2}{20\pi\varepsilon_0 R}$ দুটি ভিন্ন পদ্ধতিতে প্রতিপাদন করো: (ক) আধান স্তরায়ণ বৃদ্ধি পদ্ধতি, এবং (খ) সমগ্র স্থানে শক্তি ঘনত্ব $u_E = \frac{1}{2}\varepsilon_0 E^2$-এর সমাকলন পদ্ধতি।</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I27" t="inlineStr">
         <is>
           <t>নিরেট গোলকের স্ব-শক্তির দ্বিমুখী নিখুঁত প্রতিপাদন:</t>
@@ -2470,11 +2350,6 @@
           <t>$a, b, c$ ($a &lt; b &lt; c$) ব্যাসার্ধ বিশিষ্ট তিনটি সমকেন্দ্রী পরিবাহী পাতলা গোলকীয় খোলস যথাক্রমে $q_a, q_b, q_c$ আধানে আহিত আছে। প্রতিটি খোলসের পৃষ্ঠের বিভবের রাশিমালা নির্ণয় করো। যদি মধ্যবর্তী খোলসটিকে ($b$) ভূ-সংযুক্ত (earthed) করা হয়, তবে তার নতুন আধান $q_b'$ কত হবে?</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>সমকেন্দ্রী খোলসের বিভব ও ভূ-সংযোগের আধান নির্ণয়:</t>
@@ -2520,11 +2395,6 @@
           <t>$a$ বাহু বিশিষ্ট একটি সুষম সমবাহু ত্রিভুজের তিনটি শীর্ষবিন্দুতে তিনটি সমান বিন্দু আধান $+q$ স্থাপিত আছে। ব্যবস্থাটির মোট স্থিরবৈদ্যুতিক বিভব শক্তি কত? এই আধান তিনটির পারস্পরিক বিকর্ষণ বলের বিরুদ্ধে কাজ করে ত্রিভুজটির বাহুর দৈর্ঘ্য কমিয়ে অর্ধেক ($a/2$) করতে কত বাহ্যিক কাজ সম্পন্ন করতে হবে?</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>আধান বিন্যাসের বিভব শক্তি ও বাহ্যিক কাজ গণনা:</t>
@@ -2570,11 +2440,6 @@
           <t>ক্লাসিক্যাল ইলেকট্রন ব্যাসার্ধ (Classical Electron Radius $r_e$) কীভাবে সংজ্ঞায়িত হয়? ইলেকট্রনের সমুদয় স্থির ভর শক্তিকে ($m_e c^2$) তার স্থিরবৈদ্যুতিক স্ব-শক্তির ($U = \frac{e^2}{4\pi\varepsilon_0 r_e}$) সমতুল্য ধরে ক্লাসিক্যাল ইলেকট্রন ব্যাসার্ধের সাংখ্যিক মান নির্ণয় করো।</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I30" t="inlineStr">
         <is>
           <t>ক্লাসিক্যাল ইলেকট্রন ব্যাসার্ধ প্রতিপাদন ও সাংখ্যিক মান:</t>
@@ -2620,11 +2485,6 @@
           <t>একটি সাবান বুদ্বুদের ব্যাসার্ধ $R$ এবং আধান $Q$। সাবান পানির পৃষ্ঠটান $T_s$ হলে দেখাও যে স্থিরবৈদ্যুতিক বিকর্ষণের কারণে বুদ্বুদটি বিস্ফোরিত না হয়ে স্থিতিশীল ভারসাম্য বজায় রাখার জন্য অতিরিক্ত বায়ুর চাপ $P_{\text{in}} - P_0 = \frac{4T_s}{R} - \frac{Q^2}{32\pi^2\varepsilon_0 R^4}$। কোন শর্তে বুদ্বুদের ভেতরের চাপ বাইরের বায়ুমণ্ডলীয় চাপের সমান হবে?</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I31" t="inlineStr">
         <is>
           <t>আহিত সাবান বুদ্বুদের স্থিতিশীল ভারসাম্য সমীকরণ:</t>
@@ -2670,11 +2530,6 @@
           <t>একটি তড়িৎ দ্বিমেরুর দ্বিমেরু ভ্রামক $\vec{p} = q \vec{d}$ সংজ্ঞায়িত করো। দ্বিমেরুর অক্ষের ওপর ($E_{\text{axial}}$) এবং লম্ব সমদ্বিখণ্ডকের ওপর ($E_{\text{eq}}$) দূরবর্তী বিন্দুতে ($r \gg d$) তড়িৎ ক্ষেত্র প্রাবল্য যথাক্রমে $\frac{2p}{4\pi\varepsilon_0 r^3}$ এবং $\frac{p}{4\pi\varepsilon_0 r^3}$ প্রতিপাদন করো। দ্বিমেরুর ক্ষেত্র কেন বিন্দু আধানের চেয়ে দ্রুত হ্রাস পায় ($E \propto 1/r^3$)?</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I32" t="inlineStr">
         <is>
           <t>দ্বিমেরুর অক্ষীয় ও বিষুবীয় তড়িৎ ক্ষেত্র প্রতিপাদন:</t>
@@ -2720,11 +2575,6 @@
           <t>একটি বিন্দু দ্বিমেরুর জন্য সাধারণ বিন্দু $(r, \theta)$-তে তড়িৎ বিভব $V(r, \theta) = \frac{p\cos\theta}{4\pi\varepsilon_0 r^2}$ এবং তড়িৎ ক্ষেত্র প্রাবল্য $E(r, \theta) = \frac{p}{4\pi\varepsilon_0 r^3}\sqrt{1 + 3\cos^2\theta}$ প্রতিপাদন করো। লব্ধি তড়িৎ ক্ষেত্রটি ব্যাসার্ধ ভেক্টরের সাথে যে কোণ $\alpha$ তৈরি করে তার জন্য $\tan\alpha = \frac{1}{2}\tan\theta$ সম্পর্কটি প্রমাণ করো।</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I33" t="inlineStr">
         <is>
           <t>দ্বিমেরুর সাধারণ বিন্দুর বিভব ও ক্ষেত্র প্রতিপাদন:</t>
@@ -2770,11 +2620,6 @@
           <t>সুষম তড়িৎ ক্ষেত্র $\vec{E}$-তে স্থাপিত একটি তড়িৎ দ্বিমেরু $\vec{p}$-এর ওপর প্রযুক্ত টর্ক $\vec{\tau} = \vec{p} \times \vec{E}$ এবং স্থিতিশক্তি $U = -\vec{p}\cdot\vec{E}$ প্রতিপাদন করো। দ্বিমেরুটির স্থিতিশীল সাম্যাবস্থা এবং অস্থিতিশীল সাম্যাবস্থার কোণ কত? সুষম ক্ষেত্রে দ্বিমেরুর ওপর নিট বল কেন শূন্য হয়?</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I34" t="inlineStr">
         <is>
           <t>দ্বিমেরুর টর্ক, স্থিতিশক্তি ও সাম্যাবস্থা বিশ্লেষণ:</t>
@@ -2820,11 +2665,6 @@
           <t>জড়তার ভ্রামক $I$ বিশিষ্ট একটি তড়িৎ দ্বিমেরু $\vec{p}$ একটি সুষম তড়িৎ ক্ষেত্র $\vec{E}$-তে সাম্যাবস্থা থেকে সামান্য কোণে ($\theta \ll 1$) বিচ্যুত করে ছেড়ে দেওয়া হলো। প্রমাণ করো যে দ্বিমেরুটির গতি একটি সরল ছন্দিত স্পন্দন এবং তার কৌণিক স্পন্দনের পর্যায়কাল $T = 2\pi\sqrt{\frac{I}{pE}}$।</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I35" t="inlineStr">
         <is>
           <t>সুষম ক্ষেত্রে দ্বিমেরুর কৌণিক সরল ছন্দিত স্পন্দন:</t>
@@ -2870,11 +2710,6 @@
           <t>অসুষম তড়িৎ ক্ষেত্রে (Non-uniform electric field) একটি তড়িৎ দ্বিমেরুর ওপর প্রযুক্ত নিট বলের রাশিমালা $\vec{F} = (\vec{p}\cdot\nabla)\vec{E}$ প্রতিপাদন করো। একটি শুকনো চিরুনি দিয়ে চুল আঁচড়ানোর পর তা কেন নিরপেক্ষ কাগজের টুকরোকে আকর্ষণ করে তা দ্বিমেরু পোলারাইজেশন ও অসুষম ক্ষেত্রের ভিত্তিতে ব্যাখ্যা করো।</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I36" t="inlineStr">
         <is>
           <t>অসুষম ক্ষেত্রে বল ও নিরপেক্ষ কাগজের আকর্ষণ মেকানিজম:</t>
@@ -2920,11 +2755,6 @@
           <t>দুটি ক্ষুদ্র বিন্দু দ্বিমেরু $\vec{p}_1$ এবং $\vec{p}_2$ পরস্পর $r$ দূরত্বে তাদের সাধারণ অক্ষ বরাবর একই দিকে সমরেখীয়ভাবে (collinear) স্থাপিত আছে। প্রমাণ করো যে তাদের পারস্পরিক স্থিরবৈদ্যুতিক মিথস্ক্রিয়া স্থিতিশক্তি $U = -\frac{1}{4\pi\varepsilon_0}\frac{2p_1 p_2}{r^3}$ এবং তাদের মধ্যকার পারস্পরিক আকর্ষণ বল $F = \frac{1}{4\pi\varepsilon_0}\frac{6p_1 p_2}{r^4}$।</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I37" t="inlineStr">
         <is>
           <t>সমরেখীয় দুটি দ্বিমেরুর পারস্পরিক শক্তি ও বল প্রতিপাদন:</t>
@@ -2970,11 +2800,6 @@
           <t>যদি প্রশ্ন ৩৬-এর দ্বিমেরু দুটি সমরেখীয় না হয়ে পরস্পর সমান্তরালভাবে কিন্তু অক্ষের সাথে লম্ব অবস্থানে (parallel configuration) $r$ দূরত্বে স্থাপিত হতো, তবে তাদের মিথস্ক্রিয়া স্থিতিশক্তি ও বলের মান কত হতো? কোন বিন্যাসে দ্বিমেরুদ্বয় অধিকতর স্থিতিশীল?</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I38" t="inlineStr">
         <is>
           <t>সমান্তরাল দ্বিমেরু বিন্যাসের শক্তি ও বলের তুলনা:</t>
@@ -3020,11 +2845,6 @@
           <t>তড়িৎ চতুর্মেরু (Electric Quadrupole) কী? একটি রৈখিক চতুর্মেরু বিবেচনা করো যেখানে মূলবিন্দুতে একটি আধান $-2q$ এবং $z = \pm d$ অবস্থানে দুটি আধান $+q$ স্থাপিত। অক্ষ বরাবর দূরবর্তী বিন্দুতে ($z \gg d$) এই চতুর্মেরুর তড়িৎ বিভব $V(z) \propto 1/z^3$ এবং তড়িৎ ক্ষেত্র $E(z) \propto 1/z^4$ প্রতিপাদন করো। চতুর্মেরু ভ্রামকের সংজ্ঞা দাও।</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I39" t="inlineStr">
         <is>
           <t>তড়িৎ চতুর্মেরুর বিভব ও ক্ষেত্র প্রতিপাদন:</t>
@@ -3070,11 +2890,6 @@
           <t>একটি অসীম ভূ-সংযুক্ত সমতল পরিবাহী পাতের সামনে $d$ দূরত্বে একটি বিন্দু দ্বিমেরু $\vec{p}$ পাতের তলের সাথে লম্বভাবে স্থাপিত আছে। প্রতিবিম্ব পদ্ধতি (Method of Images) ব্যবহার করে পরিবাহী পাতটির প্রতিবিম্ব দ্বিমেরুর রূপ নির্ধারণ করো এবং পাতের দিকে দ্বিমেরুটির ওপর প্রযুক্ত আকর্ষণ বলের মান নির্ণয় করো।</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I40" t="inlineStr">
         <is>
           <t>পরিবাহী পাতের সামনে লম্ব দ্বিমেরুর প্রতিবিম্ব বল:</t>
@@ -3120,11 +2935,6 @@
           <t>পানির অণুর ($\text{H}_2\text{O}$) স্থায়ী তড়িৎ দ্বিমেরু ভ্রামক $p = 6.2 \times 10^{-30}\text{ C m}$ ($1.85\text{ Debye}$)। পানির অণুর বেন্ট জ্যামিতি ($104.5^\circ$) কীভাবে এই শক্তিশালী দ্বিমেরু ভ্রামক সৃষ্টি করে? কেন পানির ডাইইলেকট্রিক ধ্রুবক অত্যন্ত উচ্চ ($K \approx 80$) এবং কেন পানি সর্বজনীন দ্রাবক হিসেবে কাজ করে?</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I41" t="inlineStr">
         <is>
           <t>পানির অণুর স্থায়ী দ্বিমেরু ও উচ্চ পরাবৈদ্যুতিক ধ্রুবকের কারণ:</t>
@@ -3170,11 +2980,6 @@
           <t>স্থিরতড়িৎ ভারসাম্যে পরিবাহীর পাঁচটি মৌলিক ধর্ম বিবৃত ও প্রমাণ করো: (i) পরিবাহীর অভ্যন্তরে স্থির তড়িৎ ক্ষেত্র শূন্য ($\vec{E}_{\text{in}} = 0$), (ii) সমস্ত অতিরিক্ত আধান পরিবাহীর বহির্বহিঃপৃষ্ঠে অবস্থান করে, (iii) পরিবাহীর সমগ্র আয়তন ও পৃষ্ঠ একটি সমবিভব অঞ্চল, (iv) পরিবাহীর পৃষ্ঠের ঠিক বাইরে তড়িৎ ক্ষেত্র পৃষ্ঠের সাথে সর্বদা লম্ব এবং $\vec{E} = \frac{\sigma}{\varepsilon_0}\hat{n}$, এবং (v) ফাঁপা পরিবাহীর অভ্যন্তরে কোনো আধান না থাকলে সেখানে তড়িৎ ক্ষেত্র সর্বদা শূন্য (ইলেকট্রোস্ট্যাটিক শিল্ডিং)।</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I42" t="inlineStr">
         <is>
           <t>পরিবাহীর মৌলিক স্থিরবৈদ্যুতিক ধর্মের সার্বিক প্রমাণ:</t>
@@ -3220,11 +3025,6 @@
           <t>আহিত পরিবাহীর পৃষ্ঠের ওপর স্থিরবৈদ্যুতিক চাপ (Electrostatic Pressure) $P_{\text{es}} = \frac{\sigma^2}{2\varepsilon_0} = \frac{1}{2}\varepsilon_0 E^2$ প্রতিপাদন করো। প্রতিপাদনে ক্ষেত্রফল উপাদান বিবেচনায় কেন $\frac{\sigma}{\varepsilon_0}$-এর বদলে গড় ক্ষেত্র $\frac{\sigma}{2\varepsilon_0}$ ব্যবহৃত হয় তা ব্যাখ্যা করো।</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I43" t="inlineStr">
         <is>
           <t>স্থিরবৈদ্যুতিক চাপ প্রতিপাদন ও গড় ক্ষেত্রের তাৎপর্য:</t>
@@ -3270,11 +3070,6 @@
           <t>পরিবাহীর পৃষ্ঠ আধান ঘনত্ব বক্রতার ব্যাসার্ধের ব্যস্তানুপাতিক ($\sigma \propto \frac{1}{R}$)—তীক্ষ্ণ প্রান্তের ক্রিয়া (Action of Points) বা সূচিমুখের ক্রিয়া ব্যাখ্যা করো। করোনা ক্ষরণ (Corona Discharge) কী এবং বজ্রনিরোধক দণ্ডের (Lightning Rod) শীর্ষে কেন তীক্ষ্ণ সূঁচালো প্রান্ত রাখা হয়?</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I44" t="inlineStr">
         <is>
           <t>তীক্ষ্ণ প্রান্তের আধান ঘনত্ব ও করোনা ক্ষরণ মেকানিজম:</t>
@@ -3320,11 +3115,6 @@
           <t>ধারকত্বের সংজ্ঞা দাও। একটি পৃথক গোলকীয় পরিবাহীর ধারকত্ব $C = 4\pi\varepsilon_0 R$ প্রতিপাদন করো। পৃথিবীর ধারকত্ব কত? কেন একটি একক $1\text{ Farad}$ ধারকত্ব সাধারণ ল্যাবরেটরিতে একটি সাধারণ বিচ্ছিন্ন গোলক দ্বারা অর্জন করা অসম্ভব?</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I45" t="inlineStr">
         <is>
           <t>বিচ্ছিন্ন গোলকের ধারকত্ব ও ১ ফ্যারাডের বিশালতা:</t>
@@ -3421,11 +3211,6 @@
           <t>একটি গোলকীয় ধারকের (spherical capacitor) অভ্যন্তরীণ গোলকের ব্যাসার্ধ $a$ এবং বহির্বহিঃগোলকের ব্যাসার্ধ $b$ ($b &gt; a$)। (ক) বাইরের গোলকটি ভূ-সংযুক্ত থাকলে ধারকত্ব $C_1 = 4\pi\varepsilon_0 \frac{ab}{b - a}$ এবং (খ) ভেতরের গোলকটি ভূ-সংযুক্ত থাকলে ধারকত্ব $C_2 = 4\pi\varepsilon_0 \frac{b^2}{b - a}$ প্রতিপাদন করো।</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I47" t="inlineStr">
         <is>
           <t>গোলকীয় ধারকের দুই প্রকার ভূ-সংযোগের ধারকত্ব প্রতিপাদন:</t>
@@ -3471,11 +3256,6 @@
           <t>একটি সমাক্ষীয় সিলিন্ডারীয় ধারকের (cylindrical capacitor) অভ্যন্তরীণ চোঙের ব্যাসার্ধ $a$, বাইরের চোঙের ব্যাসার্ধ $b$ এবং দৈর্ঘ্য $L$ ($L \gg b$)। ধারকটির একক দৈর্ঘ্যের ধারকত্ব $\frac{C}{L} = \frac{2\pi\varepsilon_0}{\ln(b/a)}$ প্রতিপাদন করো। উচ্চ ভোল্টেজ সমাক্ষীয় কেবলে (coaxial cable) এই ধারকত্ব কীভাবে সংকেত বিকৃতি কমায়?</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I48" t="inlineStr">
         <is>
           <t>সিলিন্ডারীয় ধারকত্ব প্রতিপাদন ও কোঅ্যাক্সিয়াল কেবলের ভূমিকা:</t>
@@ -3521,11 +3301,6 @@
           <t>একটি সমান্তরাল পাত ধারকের দুটি পাতের মধ্যকার আকর্ষণ বল $F = \frac{Q^2}{2\varepsilon_0 A} = \frac{1}{2}\varepsilon_0 A E^2$ প্রতিপাদন করো। বলের সমীকরণে $\frac{Q^2}{\varepsilon_0 A}$-এর বদলে $\frac{1}{2}$ ফ্যাক্টরটি কেন আসে তা একটি পাতের নিজের দ্বারা অন্য পাতের ওপর প্রযুক্ত ক্ষেত্রের ভিত্তিতে ব্যাখ্যা করো।</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I49" t="inlineStr">
         <is>
           <t>ধারকের পাতদ্বয়ের আকর্ষণ বল ও হাফ ফ্যাক্টরের কারণ:</t>
@@ -3571,11 +3346,6 @@
           <t>একটি সমান্তরাল পাত ধারকের পাতের ক্ষেত্রফল $A$ এবং পাতদ্বয়ের মধ্যবর্তী দূরত্ব $d$। ধারকটিকে $V$ বিভব পার্থক্যের ব্যাটারির সাথে সংযুক্ত রাখা অবস্থায় পাত দুটির ব্যবধান টেনে দ্বিগুণ ($2d$) করা হলো। (i) ধারকত্ব, (ii) সঞ্চিত শক্তি, (iii) ব্যাটারি কর্তৃক সরবরাহকৃত বা শোষিত শক্তি, এবং (iv) পাত দুটি সরাতে বাহ্যিক এজেন্ট কর্তৃক সম্পাদিত কাজ নির্ণয় করো। শক্তির নিত্যতা যাচাই করো।</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I50" t="inlineStr">
         <is>
           <t>ব্যাটারি সংযুক্ত অবস্থায় পাতের ব্যবধান দ্বিগুণ করার হিসাব:</t>
@@ -3621,11 +3391,6 @@
           <t>প্রশ্ন ৪৯-এর ক্ষেত্রে যদি ব্যাটারিটি সংযোগ বিচ্ছিন্ন (disconnected) করার পর পাতের ব্যবধান দ্বিগুণ ($2d$) করা হতো, তবে (i) আধান, (ii) বিভব পার্থক্য, (iii) তড়িৎ ক্ষেত্র এবং (iv) সঞ্চিত শক্তির কী পরিবর্তন হতো? পাত দুটি সরাতে বাহ্যিক কাজ কোথা থেকে আসে?</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I51" t="inlineStr">
         <is>
           <t>ব্যাটারি বিচ্ছিন্ন অবস্থায় পাতের ব্যবধান দ্বিগুণ করার বিশ্লেষণ:</t>
@@ -3655,12 +3420,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>তড়িৎ প্রাবল্যের নিরপেক্ষ বিন্দু (Null Point)</t>
+          <t>কুলম্বের সূত্র, তড়িৎ প্রাবল্য ও দ্বিমেরু (Coulomb Law &amp; Electric Field)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -3668,32 +3433,25 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>##PRESET:dipole[size:medium]##
-বায়ুতে পরস্পর হতে $d = 50\text{{ cm}}$ দূরত্বে $q_1 = +4\text{ nC}$ এবং $q_2 = +16\text{ nC}$ মানের দুটি বিন্দু আধান স্থাপন করা হলো। আধানদ্বয়ের সংযোগকারী সরলরেখার কোন বিন্দুতে লব্ধি তড়িৎ প্রাবল্য শূন্য হবে এবং ঐ বিন্দুতে মোট তড়িৎ বিভব কত? ($k = \frac{1}{4\pi\epsilon_0} = 9 \times 10^9\text{{ N}}\cdot\text{{m}}^2/\text{{C}}^2$)</t>
+          <t>##GEO:circle[r=2.5][size:small]##
+বায়ুতে পরস্পর হতে $30\text{ cm}$ ব্যবধানে রক্ষিত দুটি বিন্দু আধান যথাক্রমে $+4.0 \times 10^{-6}\text{ C}$ এবং $-2.0 \times 10^{-6}\text{ C}$। আধানদ্বয়ের মধ্যবর্তী স্থির তড়িৎ বলের মান ও প্রকৃতি নির্ণয় কর। যদি আধান দুটিকে ডাই-ইলেকট্রিক ধ্রুবক $K = 4$ বিশিষ্ট তেলে রাখা হয়, তবে বলের মান কত হবে?</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>##PRESET:dipole[size:medium]##</t>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>ধরি $q_1$ হতে $x$ দূরত্বে প্রাবল্য শূন্য:
-$E_1 = E_2 \implies \frac{k q_1}{x^2} = \frac{k q_2}{(d - x)^2} \implies \frac{\sqrt{q_1}}{x} = \frac{\sqrt{q_2}}{d - x}$।
-$\frac{2}{x} = \frac{4}{0.5 - x} \implies 1 - 2x = 4x \implies 6x = 1 \implies x = \frac{1}{6}\text{{ m}} \approx 0.1667\text{{ m}} = 16.67\text{{ cm}}$।
-ঐ বিন্দুতে বিভব $V = k\left(\frac{q_1}{x} + \frac{q_2}{d - x}\right) = 9 \times 10^9 \left(\frac{4 \times 10^{-9}}{1/6} + \frac{16 \times 10^{-9}}{5/6}\right) = 9(24 + 19.2) = 9(43.2) = 388.8\text{{ V}}$।</t>
+          <t>কুলম্বের সূত্রানুযায়ী বায়ুতে বল $F = \frac{1}{4\pi\epsilon_0}\frac{|q_1 q_2|}{r^2} = \frac{(9.0 \times 10^9) \times (4.0 \times 10^{-6}) \times (2.0 \times 10^{-6})}{(0.30)^2} = \frac{72 \times 10^{-3}}{0.09} = 0.80\text{ N}$ (বিপরীতধর্মী হওয়ায় আকর্ষণধর্মী)। তেলে $K = 4$ হলে বল $F' = \frac{F}{K} = \frac{0.80}{4} = 0.20\text{ N}$।</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>$q_1$ হতে $16.67\text{{ cm}}$ দূরত্বে, বিভব $V = 648\text{{ V}}$</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+          <t>বায়ুতে আকর্ষণ বল $F = 0.80\text{ N}$, তেলে আকর্ষণ বল $F' = 0.20\text{ N}$</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3713,7 +3471,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ধারকত্ব, সঞ্চিত শক্তি ও সমান্তরাল পাত ধারক 2</t>
+          <t>কুলম্বের সূত্র, তড়িৎ প্রাবল্য ও দ্বিমেরু (Coulomb Law &amp; Electric Field)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3722,29 +3480,29 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>$4\ \mu\text{F}$ এবং $6\ \mu\text{F}$ ধারকত্বের দুটি ধারককে সমান্তরালে যুক্ত করে $16\text{ V}$ ব্যাটারির সাথে সংযুক্ত করা হলো। বর্তনীর তুল্য ধারকত্ব এবং উভয় ধারকে সঞ্চিত মোট তড়িৎ শক্তি কত?</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+দুটি ধনাত্মক আধান $q_1 = +9\text{ }\mu	ext{C}$ এবং $q_2 = +16\text{ }\mu	ext{C}$ পরস্পর হতে $70\text{ cm}$ দূরত্বে অবস্থিত। এদের সংযোগকারী সরলরেখার কোন বিন্দুতে লব্ধি তড়িৎ প্রাবল্যের মান শূন্য হবে?</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>$C_p = C_1 + C_2 = 4 + 6 = 10\ \mu\text{F}$।
-শক্তি $U = \frac{1}{2} C_p V^2 = 0.5 \times (10 \times 10^{-6}) \times 16^2 = 0.00128\text{ J}$।</t>
+          <t>ধরি $q_1$ হতে $x$ দূরত্বে প্রাবল্য শূন্য: $E_1 = E_2 \implies \frac{1}{4\pi\epsilon_0}\frac{q_1}{x^2} = \frac{1}{4\pi\epsilon_0}\frac{q_2}{(d - x)^2} \implies \frac{9}{x^2} = \frac{16}{(70 - x)^2}$। উভয়পক্ষে বর্গমূল নিয়ে: $\frac{3}{x} = \frac{4}{70 - x} \implies 4x = 210 - 3x \implies 7x = 210 \implies x = 30.0\text{ cm}$।</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>$C_p = 10\ \mu\text{F}, U = 0.00128\text{ J}$</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>$q_1$ হতে $30.0\text{ cm}$ দূরত্বে (বা $q_2$ হতে $40.0\text{ cm}$ দূরত্বে)</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3764,7 +3522,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ধারকত্ব, সঞ্চিত শক্তি ও সমান্তরাল পাত ধারক 3</t>
+          <t>কুলম্বের সূত্র, তড়িৎ প্রাবল্য ও দ্বিমেরু (Coulomb Law &amp; Electric Field)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3773,29 +3531,29 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>$5\ \mu\text{F}$ এবং $7\ \mu\text{F}$ ধারকত্বের দুটি ধারককে সমান্তরালে যুক্ত করে $18\text{ V}$ ব্যাটারির সাথে সংযুক্ত করা হলো। বর্তনীর তুল্য ধারকত্ব এবং উভয় ধারকে সঞ্চিত মোট তড়িৎ শক্তি কত?</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>##GEO:triangle[b=3,h=3][size:small]##
+একটি সমবাহু ত্রিভুজের তিনটি শীর্ষবিন্দু $A, B, C$-এর প্রতি বাহুর দৈর্ঘ্য $a = 20\text{ cm}$। $A$ ও $B$ বিন্দুতে যথাক্রমে $+5.0\text{ }\mu	ext{C}$ ও $-5.0\text{ }\mu	ext{C}$ আধান রাখা হলো। তৃতীয় শীর্ষবিন্দু $C$-তে লব্ধি তড়িৎ প্রাবল্য কত হবে?</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>##GEO:triangle[b=3,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>$C_p = C_1 + C_2 = 5 + 7 = 12\ \mu\text{F}$।
-শক্তি $U = \frac{1}{2} C_p V^2 = 0.5 \times (12 \times 10^{-6}) \times 18^2 = 0.00194\text{ J}$।</t>
+          <t>প্রতিটি আধানের দরুন প্রাবল্য $E_0 = \frac{kq}{a^2} = \frac{(9 \times 10^9)(5 \times 10^{-6})}{(0.20)^2} = \frac{45000}{0.04} = 1.125 \times 10^6\text{ N/C}$। $C$ বিন্দুতে ধনাত্মক আধানের দরুন প্রাবল্য বহির্মুখী এবং ঋণাত্মক আধানের দরুন অন্তর্মুখী। এদের মধ্যবর্তী কোণ $\theta = 180^\circ - 60^\circ = 120^\circ$। লব্ধি $E = \sqrt{E_0^2 + E_0^2 + 2E_0^2 \cos 120^\circ} = E_0 = 1.125 \times 10^6\text{ N/C}$।</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>$C_p = 12\ \mu\text{F}, U = 0.00194\text{ J}$</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+          <t>লব্ধি প্রাবল্য $E = 1.125 \times 10^6\text{ N/C}$ ($AB$-এর সমান্তরালে $A \to B$ অভিমুখে)</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3815,7 +3573,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ধারকত্ব, সঞ্চিত শক্তি ও সমান্তরাল পাত ধারক 4</t>
+          <t>কুলম্বের সূত্র, তড়িৎ প্রাবল্য ও দ্বিমেরু (Coulomb Law &amp; Electric Field)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3824,34 +3582,29 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>##PRESET:circuit-resistors[size:medium]##
-$6\ \mu\text{F}$ এবং $8\ \mu\text{F}$ ধারকত্বের দুটি ধারককে সমান্তরালে যুক্ত করে $20\text{ V}$ ব্যাটারির সাথে সংযুক্ত করা হলো। বর্তনীর তুল্য ধারকত্ব এবং উভয় ধারকে সঞ্চিত মোট তড়িৎ শক্তি কত?</t>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি ইলেকট্রন ($m = 9.11 \times 10^{-31}\text{ kg}, q = 1.6 \times 10^{-19}\text{ C}$) একটি সুষম তড়িৎ ক্ষেত্র $E = 2.0 \times 10^4\text{ N/C}$-এ স্থির অবস্থা হতে ত্বরাম্বিত হয়। $1.5\text{ cm}$ দূরত্ব অতিক্রম করার পর ইলেকট্রনটির বেগ কত হবে? (অভিকর্ষের প্রভাব অগ্রাহ্য কর)।</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>##PRESET:circuit-resistors[size:medium]##</t>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>$C_p = C_1 + C_2 = 6 + 8 = 14\ \mu\text{F}$।
-শক্তি $U = \frac{1}{2} C_p V^2 = 0.5 \times (14 \times 10^{-6}) \times 20^2 = 0.0028\text{ J}$।</t>
+          <t>ত্বরণ $a = \frac{qE}{m} = \frac{(1.6 \times 10^{-19})(2.0 \times 10^4)}{9.11 \times 10^{-31}} = \frac{3.2 \times 10^{-15}}{9.11 \times 10^{-31}} \approx 3.5126 \times 10^{15}\text{ m/s}^2$। দূরত্ব $s = 0.015\text{ m}$। $v^2 = 2as \implies v = \sqrt{2 \times (3.5126 \times 10^{15}) \times 0.015} = \sqrt{1.0538 \times 10^{14}} \approx 1.0265 \times 10^7\text{ m/s}$।</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>$C_p = 14\ \mu\text{F}, U = 0.0028\text{ J}$</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+          <t>বেগ $v = 1.026 \times 10^7\text{ m/s}$</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3871,7 +3624,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ধারকত্ব, সঞ্চিত শক্তি ও সমান্তরাল পাত ধারক 5</t>
+          <t>কুলম্বের সূত্র, তড়িৎ প্রাবল্য ও দ্বিমেরু (Coulomb Law &amp; Electric Field)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3880,29 +3633,29 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>$7\ \mu\text{F}$ এবং $9\ \mu\text{F}$ ধারকত্বের দুটি ধারককে সমান্তরালে যুক্ত করে $22\text{ V}$ ব্যাটারির সাথে সংযুক্ত করা হলো। বর্তনীর তুল্য ধারকত্ব এবং উভয় ধারকে সঞ্চিত মোট তড়িৎ শক্তি কত?</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি তড়িৎ দ্বিমেরুর আধানদ্বয় $\pm 2.0\text{ }\mu	ext{C}$ এবং এদের মধ্যবর্তী দূরত্ব $2a = 4.0\text{ cm}$। দ্বিমেরুটির দ্বিমেরু ভ্রামক $p$ কত? দ্বিমেরুর কেন্দ্র হতে অক্ষীয় অবস্থানে (End-on position) $20\text{ cm}$ দূরে তড়িৎ প্রাবল্য নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>$C_p = C_1 + C_2 = 7 + 9 = 16\ \mu\text{F}$।
-শক্তি $U = \frac{1}{2} C_p V^2 = 0.5 \times (16 \times 10^{-6}) \times 22^2 = 0.00387\text{ J}$।</t>
+          <t>দ্বিমেরু ভ্রামক $p = q(2a) = (2.0 \times 10^{-6}\text{ C}) \times (0.04\text{ m}) = 8.0 \times 10^{-8}\text{ C}\cdot\text{m}$। দূরবর্তী অক্ষীয় প্রাবল্য $E = \frac{1}{4\pi\epsilon_0}\frac{2p}{r^3} = \frac{(9.0 \times 10^9) \times 2(8.0 \times 10^{-8})}{(0.20)^3} = \frac{1440}{0.008} = 1.80 \times 10^5\text{ N/C}$।</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>$C_p = 16\ \mu\text{F}, U = 0.00387\text{ J}$</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+          <t>দ্বিমেরু ভ্রামক $p = 8.0 \times 10^{-8}\text{ C}\cdot\text{m}$, প্রাবল্য $E = 1.80 \times 10^5\text{ N/C}$</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3922,7 +3675,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ধারকত্ব, সঞ্চিত শক্তি ও সমান্তরাল পাত ধারক 6</t>
+          <t>কুলম্বের সূত্র, তড়িৎ প্রাবল্য ও দ্বিমেরু (Coulomb Law &amp; Electric Field)</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3931,29 +3684,29 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>$8\ \mu\text{F}$ এবং $4\ \mu\text{F}$ ধারকত্বের দুটি ধারককে সমান্তরালে যুক্ত করে $24\text{ V}$ ব্যাটারির সাথে সংযুক্ত করা হলো। বর্তনীর তুল্য ধারকত্ব এবং উভয় ধারকে সঞ্চিত মোট তড়িৎ শক্তি কত?</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+উপরের দ্বিমেরুটির কেন্দ্র হতে নিরক্ষীয় অবস্থানে (Broadside-on position) একই দূরত্বে ($20\text{ cm}$) তড়িৎ প্রাবল্য কত হবে?</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>$C_p = C_1 + C_2 = 8 + 4 = 12\ \mu\text{F}$।
-শক্তি $U = \frac{1}{2} C_p V^2 = 0.5 \times (12 \times 10^{-6}) \times 24^2 = 0.00346\text{ J}$।</t>
+          <t>নিরক্ষীয় প্রাবল্য অক্ষীয় প্রাবল্যের অর্ধেক: $E_{\text{eq}} = \frac{1}{4\pi\epsilon_0}\frac{p}{r^3} = \frac{1}{2}E_{\text{axial}} = \frac{1.80 \times 10^5}{2} = 9.0 \times 10^4\text{ N/C}$।</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>$C_p = 12\ \mu\text{F}, U = 0.00346\text{ J}$</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>নিরক্ষীয় প্রাবল্য $E_{\text{eq}} = 9.0 \times 10^4\text{ N/C}$</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3973,7 +3726,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ধারকত্ব, সঞ্চিত শক্তি ও সমান্তরাল পাত ধারক 7</t>
+          <t>কুলম্বের সূত্র, তড়িৎ প্রাবল্য ও দ্বিমেরু (Coulomb Law &amp; Electric Field)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3982,29 +3735,29 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>$9\ \mu\text{F}$ এবং $5\ \mu\text{F}$ ধারকত্বের দুটি ধারককে সমান্তরালে যুক্ত করে $26\text{ V}$ ব্যাটারির সাথে সংযুক্ত করা হলো। বর্তনীর তুল্য ধারকত্ব এবং উভয় ধারকে সঞ্চিত মোট তড়িৎ শক্তি কত?</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি সুষম তড়িৎ ক্ষেত্রে $E = 5.0 \times 10^4\text{ N/C}$ একটি দ্বিমেরু ভ্রামক $p = 4.0 \times 10^{-29}\text{ C}\cdot	ext{m}$-কে ক্ষেত্রের সাথে $30^\circ$ কোণে রাখা হলো। দ্বিমেরুর ওপর প্রযুক্ত টর্ক $\tau$ এবং এটিকে $0^\circ$ হতে $180^\circ$ কোণে ঘোরাতে কৃতকাজ নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>$C_p = C_1 + C_2 = 9 + 5 = 14\ \mu\text{F}$।
-শক্তি $U = \frac{1}{2} C_p V^2 = 0.5 \times (14 \times 10^{-6}) \times 26^2 = 0.00473\text{ J}$।</t>
+          <t>টর্ক $\tau = p E \sin\theta = (4.0 \times 10^{-29}) \times (5.0 \times 10^4) \times \sin 30^\circ = 2.0 \times 10^{-24} \times 0.5 = 1.0 \times 10^{-24}\text{ N}\cdot\text{m}$। ঘোরাতে কৃতকাজ $W = -pE(\cos 180^\circ - \cos 0^\circ) = -pE(-1 - 1) = 2pE = 2 \times (2.0 \times 10^{-24}) = 4.0 \times 10^{-24}\text{ J}$।</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>$C_p = 14\ \mu\text{F}, U = 0.00473\text{ J}$</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+          <t>টর্ক $\tau = 1.0 \times 10^{-24}\text{ N}\cdot\text{m}$, কৃতকাজ $W = 4.0 \times 10^{-24}\text{ J}$</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4024,7 +3777,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ধারকত্ব, সঞ্চিত শক্তি ও সমান্তরাল পাত ধারক 8</t>
+          <t>কুলম্বের সূত্র, তড়িৎ প্রাবল্য ও দ্বিমেরু (Coulomb Law &amp; Electric Field)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4033,34 +3786,29 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>##PRESET:circuit-resistors[size:medium]##
-$2\ \mu\text{F}$ এবং $6\ \mu\text{F}$ ধারকত্বের দুটি ধারককে সমান্তরালে যুক্ত করে $28\text{ V}$ ব্যাটারির সাথে সংযুক্ত করা হলো। বর্তনীর তুল্য ধারকত্ব এবং উভয় ধারকে সঞ্চিত মোট তড়িৎ শক্তি কত?</t>
+          <t>##GEO:triangle[b=3,h=4][size:small]##
+সমান ভরের ($m = 10\text{ g}$) দুটি ক্ষুদ্র গোলককে একই বিন্দু হতে দুটি $L = 1.0\text{ m}$ দৈর্ঘ্যের সিল্ক সুতা দ্বারা ঝুলিয়ে সমান আধান $q$ দেওয়া হলো। বিকর্ষণের ফলে এরা পরস্পর হতে $x = 10\text{ cm}$ দূরত্বে স্থির থাকলে প্রতিটি গোলকের আধান $q$ কত কুলম্ব? ($g = 9.8\text{ ms}^{-2}$)।</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>##PRESET:circuit-resistors[size:medium]##</t>
+          <t>##GEO:triangle[b=3,h=4][size:small]##</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>$C_p = C_1 + C_2 = 2 + 6 = 8\ \mu\text{F}$।
-শক্তি $U = \frac{1}{2} C_p V^2 = 0.5 \times (8 \times 10^{-6}) \times 28^2 = 0.00314\text{ J}$।</t>
+          <t>সাম্যাবস্থায় $\tan\theta = \frac{F_e}{mg} \approx \sin\theta = \frac{x/2}{L} = \frac{0.05}{1.0} = 0.05$। কুলম্ব বল $F_e = mg \tan\theta = (0.010)(9.8)(0.05) = 4.9 \times 10^{-3}\text{ N}$। আবার $F_e = \frac{kq^2}{x^2} \implies 4.9 \times 10^{-3} = \frac{(9 \times 10^9)q^2}{(0.10)^2} = \frac{9 \times 10^9 q^2}{0.01} = 9 \times 10^{11} q^2$। $q^2 = \frac{4.9 \times 10^{-3}}{9 \times 10^{11}} = 5.444 \times 10^{-15} \implies q \approx 2.33 \times 10^{-8}\text{ C} \approx 23.3\text{ nC}$।</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>$C_p = 8\ \mu\text{F}, U = 0.00314\text{ J}$</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+          <t>আধান $q = 2.32 \times 10^{-8}\text{ C} \approx 23.2\text{ nC}$</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4080,7 +3828,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ধারকত্ব, সঞ্চিত শক্তি ও সমান্তরাল পাত ধারক 9</t>
+          <t>কুলম্বের সূত্র, তড়িৎ প্রাবল্য ও দ্বিমেরু (Coulomb Law &amp; Electric Field)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4089,29 +3837,29 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>$3\ \mu\text{F}$ এবং $7\ \mu\text{F}$ ধারকত্বের দুটি ধারককে সমান্তরালে যুক্ত করে $30\text{ V}$ ব্যাটারির সাথে সংযুক্ত করা হলো। বর্তনীর তুল্য ধারকত্ব এবং উভয় ধারকে সঞ্চিত মোট তড়িৎ শক্তি কত?</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>##GEO:circle[r=3][size:small]##
+একটি সুষম ত্বরিত গোলকের ব্যাসার্ধ $R = 10\text{ cm}$ এবং এতে $Q = +2.0\text{ }\mu	ext{C}$ আধান পরিবাহী তলে সুষমভাবে বণ্টিত। কেন্দ্র হতে (ক) $r = 5\text{ cm}$ (ভেতরে), (খ) $r = 10\text{ cm}$ (পৃষ্ঠে), এবং (গ) $r = 20\text{ cm}$ (বাইরে) বিন্দুতে তড়িৎ প্রাবল্য কত?</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>$C_p = C_1 + C_2 = 3 + 7 = 10\ \mu\text{F}$।
-শক্তি $U = \frac{1}{2} C_p V^2 = 0.5 \times (10 \times 10^{-6}) \times 30^2 = 0.0045\text{ J}$।</t>
+          <t>(ক) পরিবাহীর অভ্যন্তরে কোনো আধান না থাকায় গাউসের সূত্রানুসারে তড়িৎ প্রাবল্য শূন্য: $E_{\text{in}} = 0$। (খ) পৃষ্ঠে: $E = \frac{kQ}{R^2} = \frac{(9 \times 10^9)(2 \times 10^{-6})}{(0.10)^2} = \frac{18000}{0.01} = 1.80 \times 10^6\text{ N/C}$। (গ) বাইরে $r = 0.20\text{ m}$: $E = \frac{kQ}{r^2} = \frac{18000}{(0.20)^2} = \frac{18000}{0.04} = 4.50 \times 10^5\text{ N/C}$।</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>$C_p = 10\ \mu\text{F}, U = 0.0045\text{ J}$</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+          <t>(ক) $E_{\text{in}} = 0$, (খ) $E_{\text{surface}} = 1.80 \times 10^6\text{ N/C}$, (গ) $E_{\text{out}} = 4.50 \times 10^5\text{ N/C}$</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4131,7 +3879,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ধারকত্ব, সঞ্চিত শক্তি ও সমান্তরাল পাত ধারক 10</t>
+          <t>কুলম্বের সূত্র, তড়িৎ প্রাবল্য ও দ্বিমেরু (Coulomb Law &amp; Electric Field)</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4140,29 +3888,29 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>$4\ \mu\text{F}$ এবং $8\ \mu\text{F}$ ধারকত্বের দুটি ধারককে সমান্তরালে যুক্ত করে $12\text{ V}$ ব্যাটারির সাথে সংযুক্ত করা হলো। বর্তনীর তুল্য ধারকত্ব এবং উভয় ধারকে সঞ্চিত মোট তড়িৎ শক্তি কত?</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+মিলিকানের তেল বিন্দু পরীক্ষায় $m = 3.2 \times 10^{-14}\text{ kg}$ ভরের একটি তেল বিন্দু $d = 2.0\text{ cm}$ ব্যবধানে থাকা দুটি অনুভূমিক পাতের মধ্যে স্থিরভাবে ভাসমান। পাতদ্বয়ের বিভব পার্থক্য $V = 980\text{ V}$ হলে তেল বিন্দুটিতে কয়টি অতিরিক্ত ইলেকট্রন রয়েছে? ($g = 9.8\text{ ms}^{-2}, e = 1.6 \times 10^{-19}\text{ C}$)।</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>$C_p = C_1 + C_2 = 4 + 8 = 12\ \mu\text{F}$।
-শক্তি $U = \frac{1}{2} C_p V^2 = 0.5 \times (12 \times 10^{-6}) \times 12^2 = 0.00086\text{ J}$।</t>
+          <t>তড়িৎ ক্ষেত্র $E = \frac{V}{d} = \frac{980}{0.02} = 49000\text{ V/m}$। ভাসমান অবস্থায় তড়িৎ বল ও ওজন সমান: $qE = mg \implies q = \frac{mg}{E} = \frac{(3.2 \times 10^{-14})(9.8)}{49000} = \frac{3.136 \times 10^{-13}}{49000} = 6.40 \times 10^{-18}\text{ C}$। ইলেকট্রন সংখ্যা $n = \frac{q}{e} = \frac{6.40 \times 10^{-18}}{1.6 \times 10^{-19}} = 40$।</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>$C_p = 12\ \mu\text{F}, U = 0.00086\text{ J}$</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+          <t>ইলেকট্রন সংখ্যা $n = 40$ টি</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4182,38 +3930,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ধারকত্ব, সঞ্চিত শক্তি ও সমান্তরাল পাত ধারক 11</t>
+          <t>তড়িৎ বিভব, কৃতকাজ ও স্থির তড়িৎ শক্তি (Electric Potential &amp; Energy)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>$5\ \mu\text{F}$ এবং $9\ \mu\text{F}$ ধারকত্বের দুটি ধারককে সমান্তরালে যুক্ত করে $14\text{ V}$ ব্যাটারির সাথে সংযুক্ত করা হলো। বর্তনীর তুল্য ধারকত্ব এবং উভয় ধারকে সঞ্চিত মোট তড়িৎ শক্তি কত?</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr"/>
+          <t>##GEO:rect[w=3,h=3][size:small]##
+একটি বর্গক্ষেত্রের প্রতি বাহুর দৈর্ঘ্য $a = 1.0\text{ m}$। এর চারটি শীর্ষবিন্দুতে যথাক্রমে $+2.0\text{ }\mu	ext{C}, -3.0\text{ }\mu	ext{C}, +4.0\text{ }\mu	ext{C}$ এবং $-1.0\text{ }\mu	ext{C}$ আধান স্থাপন করা হলো। বর্গক্ষেত্রের কেন্দ্রবিন্দুতে মোট তড়িৎ বিভব $V$ কত?</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=3,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>$C_p = C_1 + C_2 = 5 + 9 = 14\ \mu\text{F}$।
-শক্তি $U = \frac{1}{2} C_p V^2 = 0.5 \times (14 \times 10^{-6}) \times 14^2 = 0.00137\text{ J}$।</t>
+          <t>শীর্ষ হতে কেন্দ্রের দূরত্ব $r = \frac{a}{\sqrt{2}} = \frac{1.0}{\sqrt{2}} \approx 0.7071\text{ m}$। কেন্দ্রবিন্দুতে স্কেলার বিভবের সমষ্টি: $V = \frac{k}{r}\sum q_i = \frac{9.0 \times 10^9}{1/\sqrt{2}}(2 - 3 + 4 - 1) \times 10^{-6} = (9 \times 10^3 \times \sqrt{2})(2.0) = 18000\sqrt{2} \approx 25455.8\text{ V} \approx 25.46\text{ kV}$।</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>$C_p = 14\ \mu\text{F}, U = 0.00137\text{ J}$</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+          <t>কেন্দ্রে মোট বিভব $V = 2.546 \times 10^4\text{ V} \approx 25.46\text{ kV}$</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4233,43 +3981,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ধারকত্ব, সঞ্চিত শক্তি ও সমান্তরাল পাত ধারক 12</t>
+          <t>তড়িৎ বিভব, কৃতকাজ ও স্থির তড়িৎ শক্তি (Electric Potential &amp; Energy)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>##PRESET:circuit-resistors[size:medium]##
-$6\ \mu\text{F}$ এবং $4\ \mu\text{F}$ ধারকত্বের দুটি ধারককে সমান্তরালে যুক্ত করে $16\text{ V}$ ব্যাটারির সাথে সংযুক্ত করা হলো। বর্তনীর তুল্য ধারকত্ব এবং উভয় ধারকে সঞ্চিত মোট তড়িৎ শক্তি কত?</t>
+          <t>##GEO:circle[r=3][size:small]##
+একটি গোলীয় পরিবাহীর ব্যাসার্ধ $R = 15\text{ cm}$ এবং পৃষ্ঠের বিভব $300\text{ V}$। গোলকটির কেন্দ্র হতে (ক) $10\text{ cm}$ দূরে এবং (খ) $30\text{ cm}$ দূরে বিভবের মান কত?</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>##PRESET:circuit-resistors[size:medium]##</t>
+          <t>##GEO:circle[r=3][size:small]##</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>$C_p = C_1 + C_2 = 6 + 4 = 10\ \mu\text{F}$।
-শক্তি $U = \frac{1}{2} C_p V^2 = 0.5 \times (10 \times 10^{-6}) \times 16^2 = 0.00128\text{ J}$।</t>
+          <t>(ক) পরিবাহীর অভ্যন্তরে প্রাবল্য শূন্য হওয়ায় পৃষ্ঠ হতে কেন্দ্র পর্যন্ত সর্বত্র বিভব পৃষ্ঠের বিভবের সমান থাকে: $V(10\text{ cm}) = V_{\text{surface}} = 300.0\text{ V}$। (খ) বাইরে বিভব দূরত্বের ব্যস্তানুপাতিক: $V_{\text{out}} = V_{\text{surface}} \frac{R}{r} = 300 \times \frac{15}{30} = 150.0\text{ V}$।</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>$C_p = 10\ \mu\text{F}, U = 0.00128\text{ J}$</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+          <t>(ক) অভ্যন্তরে $V_{\text{in}} = 300.0\text{ V}$, (খ) বাইরে $V_{\text{out}} = 150.0\text{ V}$</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4289,38 +4032,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ধারকত্ব, সঞ্চিত শক্তি ও সমান্তরাল পাত ধারক 13</t>
+          <t>তড়িৎ বিভব, কৃতকাজ ও স্থির তড়িৎ শক্তি (Electric Potential &amp; Energy)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>$7\ \mu\text{F}$ এবং $5\ \mu\text{F}$ ধারকত্বের দুটি ধারককে সমান্তরালে যুক্ত করে $18\text{ V}$ ব্যাটারির সাথে সংযুক্ত করা হলো। বর্তনীর তুল্য ধারকত্ব এবং উভয় ধারকে সঞ্চিত মোট তড়িৎ শক্তি কত?</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+তড়িৎ ক্ষেত্রের বিভব ফাংশন $V(x,y,z) = 4x^2 - 3y^2 + 2z\text{ ভোল্ট}$। $(1, -2, 3)$ বিন্দুতে তড়িৎ প্রাবল্যের ভেক্টর রূপ $\vec{E}$ এবং এর পরম মান নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>$C_p = C_1 + C_2 = 7 + 5 = 12\ \mu\text{F}$।
-শক্তি $U = \frac{1}{2} C_p V^2 = 0.5 \times (12 \times 10^{-6}) \times 18^2 = 0.00194\text{ J}$।</t>
+          <t>$\vec{E} = -\nabla V = -\left(\frac{\partial V}{\partial x}\hat{i} + \frac{\partial V}{\partial y}\hat{j} + \frac{\partial V}{\partial z}\hat{k}\right) = -(8x\hat{i} - 6y\hat{j} + 2\hat{k}) = -8x\hat{i} + 6y\hat{j} - 2\hat{k}$। $(1, -2, 3)$ বিন্দুতে: $\vec{E} = -8(1)\hat{i} + 6(-2)\hat{j} - 2\hat{k} = -8\hat{i} - 12\hat{j} - 2\hat{k}\text{ V/m}$। মান $E = \sqrt{(-8)^2 + (-12)^2 + (-2)^2} = \sqrt{64 + 144 + 4} = \sqrt{212} \approx 14.56\text{ V/m}$।</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>$C_p = 12\ \mu\text{F}, U = 0.00194\text{ J}$</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+          <t>$\vec{E} = (-8\hat{i} - 12\hat{j} - 2\hat{k})\text{ V/m}$, মান $E = 14.56\text{ V/m}$</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4340,38 +4083,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ধারকত্ব, সঞ্চিত শক্তি ও সমান্তরাল পাত ধারক 14</t>
+          <t>তড়িৎ বিভব, কৃতকাজ ও স্থির তড়িৎ শক্তি (Electric Potential &amp; Energy)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>$8\ \mu\text{F}$ এবং $6\ \mu\text{F}$ ধারকত্বের দুটি ধারককে সমান্তরালে যুক্ত করে $20\text{ V}$ ব্যাটারির সাথে সংযুক্ত করা হলো। বর্তনীর তুল্য ধারকত্ব এবং উভয় ধারকে সঞ্চিত মোট তড়িৎ শক্তি কত?</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##
+দুটি সমান্তরাল পাতের বিভব যথাক্রমে $+100\text{ V}$ এবং $-100\text{ V}$। পাতদ্বয়ের মধ্যবর্তী ব্যবধান $d = 4.0\text{ cm}$ হলে পাতের মধ্যবর্তী স্থানে সুষম তড়িৎ প্রাবল্য কত? একটি প্রোটনকে এক পাত হতে অপর পাতে স্থানান্তরিত করতে কত কাজ সম্পন্ন হবে?</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>$C_p = C_1 + C_2 = 8 + 6 = 14\ \mu\text{F}$।
-শক্তি $U = \frac{1}{2} C_p V^2 = 0.5 \times (14 \times 10^{-6}) \times 20^2 = 0.0028\text{ J}$।</t>
+          <t>বিভব পার্থক্য $\Delta V = 100 - (-100) = 200.0\text{ V}$। প্রাবল্য $E = \frac{\Delta V}{d} = \frac{200}{0.04} = 5000.0\text{ V/m}$। প্রোটনের আধান $q = 1.6 \times 10^{-19}\text{ C}$। কৃতকাজ $W = q\Delta V = (1.6 \times 10^{-19}\text{ C}) \times (200\text{ V}) = 3.20 \times 10^{-17}\text{ J} = 200.0\text{ eV}$।</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>$C_p = 14\ \mu\text{F}, U = 0.0028\text{ J}$</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+          <t>তড়িৎ প্রাবল্য $E = 5000.0\text{ V/m}$, কৃতকাজ $W = 3.20 \times 10^{-17}\text{ J} = 200.0\text{ eV}$</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4391,38 +4134,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ধারকত্ব, সঞ্চিত শক্তি ও সমান্তরাল পাত ধারক 15</t>
+          <t>তড়িৎ বিভব, কৃতকাজ ও স্থির তড়িৎ শক্তি (Electric Potential &amp; Energy)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>$9\ \mu\text{F}$ এবং $7\ \mu\text{F}$ ধারকত্বের দুটি ধারককে সমান্তরালে যুক্ত করে $22\text{ V}$ ব্যাটারির সাথে সংযুক্ত করা হলো। বর্তনীর তুল্য ধারকত্ব এবং উভয় ধারকে সঞ্চিত মোট তড়িৎ শক্তি কত?</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+$64$টি অভিন্ন পারদ ফোঁটা যাদের প্রত্যেকের বিভব $10\text{ V}$, একত্রিত হয়ে একটি বড় ফোঁটায় পরিণত হলো। বড় ফোঁটাটির তল বিভব কত হবে?</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>$C_p = C_1 + C_2 = 9 + 7 = 16\ \mu\text{F}$।
-শক্তি $U = \frac{1}{2} C_p V^2 = 0.5 \times (16 \times 10^{-6}) \times 22^2 = 0.00387\text{ J}$।</t>
+          <t>আয়তন সংরক্ষণ: $\frac{4}{3}\pi R^3 = 64 \times \frac{4}{3}\pi r^3 \implies R = 64^{1/3} r = 4r$। আধান সংরক্ষণ: $Q = 64 q$। বিভব $V = \frac{kQ}{R} = \frac{k(64q)}{4r} = 16 \left(\frac{kq}{r}\right) = 16 \times 10 = 160.0\text{ V}$ (সাধারণ সূত্র: $V_{\text{big}} = n^{2/3} V_{\text{small}} = 64^{2/3}(10) = 16 \times 10 = 160.0\text{ V}$)।</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>$C_p = 16\ \mu\text{F}, U = 0.00387\text{ J}$</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+          <t>বড় ফোঁটার বিভব $V_{\text{big}} = 160.0\text{ V}$</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4442,43 +4185,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ধারকত্ব, সঞ্চিত শক্তি ও সমান্তরাল পাত ধারক 16</t>
+          <t>তড়িৎ বিভব, কৃতকাজ ও স্থির তড়িৎ শক্তি (Electric Potential &amp; Energy)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>##PRESET:circuit-resistors[size:medium]##
-$2\ \mu\text{F}$ এবং $8\ \mu\text{F}$ ধারকত্বের দুটি ধারককে সমান্তরালে যুক্ত করে $24\text{ V}$ ব্যাটারির সাথে সংযুক্ত করা হলো। বর্তনীর তুল্য ধারকত্ব এবং উভয় ধারকে সঞ্চিত মোট তড়িৎ শক্তি কত?</t>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি আলফা কণাকে ($q = +2e, m = 6.64 \times 10^{-27}\text{ kg}$) $V = 1.0 	imes 10^6\text{ V}$ বিভব পার্থক্যের মধ্য দিয়ে ত্বরাম্বিত করা হলো। কণাটির অর্জিত গতিশক্তি জুল ও মেগা-ইলেকট্রন ভোল্টে ($	ext{MeV}$) এবং অর্জিত বেগ কত হবে?</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>##PRESET:circuit-resistors[size:medium]##</t>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>$C_p = C_1 + C_2 = 2 + 8 = 10\ \mu\text{F}$।
-শক্তি $U = \frac{1}{2} C_p V^2 = 0.5 \times (10 \times 10^{-6}) \times 24^2 = 0.00288\text{ J}$।</t>
+          <t>গতিশক্তি $E_k = q V = (2 \times 1.6 \times 10^{-19}\text{ C}) \times 10^6\text{ V} = 3.20 \times 10^{-13}\text{ J} = 2.0\text{ MeV}$। বেগ $v = \sqrt{\frac{2E_k}{m}} = \sqrt{\frac{2 \times 3.20 \times 10^{-13}}{6.64 \times 10^{-27}}} = \sqrt{9.6385 \times 10^{13}} \approx 9.8176 \times 10^6\text{ m/s}$।</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>$C_p = 10\ \mu\text{F}, U = 0.00288\text{ J}$</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+          <t>গতিশক্তি $E_k = 3.20 \times 10^{-13}\text{ J} = 2.0\text{ MeV}$, বেগ $v = 9.82 \times 10^6\text{ m/s}$</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4498,38 +4236,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>ধারকত্ব, সঞ্চিত শক্তি ও সমান্তরাল পাত ধারক 17</t>
+          <t>তড়িৎ বিভব, কৃতকাজ ও স্থির তড়িৎ শক্তি (Electric Potential &amp; Energy)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>$3\ \mu\text{F}$ এবং $9\ \mu\text{F}$ ধারকত্বের দুটি ধারককে সমান্তরালে যুক্ত করে $26\text{ V}$ ব্যাটারির সাথে সংযুক্ত করা হলো। বর্তনীর তুল্য ধারকত্ব এবং উভয় ধারকে সঞ্চিত মোট তড়িৎ শক্তি কত?</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+          <t>##GEO:triangle[b=3,h=3][size:small]##
+তিনটি বিন্দু আধান $+q, +q$ এবং $-2q$-কে $a$ বাহুবিশিষ্ট সমবাহু ত্রিভুজের তিনটি শীর্ষবিন্দুতে স্থাপন করা হলো। ব্যবস্থাটির মোট স্থির তড়িৎ স্থিতিশক্তি (Electrostatic potential energy) কত?</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>##GEO:triangle[b=3,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>$C_p = C_1 + C_2 = 3 + 9 = 12\ \mu\text{F}$।
-শক্তি $U = \frac{1}{2} C_p V^2 = 0.5 \times (12 \times 10^{-6}) \times 26^2 = 0.00406\text{ J}$।</t>
+          <t>তিন জোড়া আধানের বিভব শক্তির সমষ্টি: $U = U_{12} + U_{23} + U_{31} = \frac{k(q)(q)}{a} + \frac{k(q)(-2q)}{a} + \frac{k(q)(-2q)}{a} = \frac{k q^2}{a} - \frac{2k q^2}{a} - \frac{2k q^2}{a} = -\frac{3 k q^2}{a}$।</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>$C_p = 12\ \mu\text{F}, U = 0.00406\text{ J}$</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+          <t>মোট স্থিতিশক্তি $U = -\frac{3 k q^2}{a}$</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4549,38 +4287,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ধারকত্ব, সঞ্চিত শক্তি ও সমান্তরাল পাত ধারক 18</t>
+          <t>তড়িৎ বিভব, কৃতকাজ ও স্থির তড়িৎ শক্তি (Electric Potential &amp; Energy)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>$4\ \mu\text{F}$ এবং $4\ \mu\text{F}$ ধারকত্বের দুটি ধারককে সমান্তরালে যুক্ত করে $28\text{ V}$ ব্যাটারির সাথে সংযুক্ত করা হলো। বর্তনীর তুল্য ধারকত্ব এবং উভয় ধারকে সঞ্চিত মোট তড়িৎ শক্তি কত?</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+একটি সমবিভব তলের (Equipotential surface) বৈশিষ্ট্য: সমবিভব তলের ওপর যেকোনো দুটি বিন্দুর মধ্যে একটি আধানকে স্থানান্তরিত করতে কত কাজ সম্পন্ন হয় এবং তড়িৎ বলরেখাগুলো সমবিভব তলকে কত কোণে ছেদ করে?</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>$C_p = C_1 + C_2 = 4 + 4 = 8\ \mu\text{F}$।
-শক্তি $U = \frac{1}{2} C_p V^2 = 0.5 \times (8 \times 10^{-6}) \times 28^2 = 0.00314\text{ J}$।</t>
+          <t>সমবিভব তলে সকল বিন্দুর বিভব সমান ($V_A = V_B$), ফলে বিভব পার্থক্য $\Delta V = 0$। কাজ $W = q\Delta V = 0$। আবার $dW = -\vec{E}\cdot d\vec{r} = -E dr \cos\theta = 0 \implies \cos\theta = 0 \implies \theta = 90^\circ$। ফলে তড়িৎ বলরেখা সমবিভব তলের সাথে সর্বদা লম্বভাবে অবস্থান করে।</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>$C_p = 8\ \mu\text{F}, U = 0.00314\text{ J}$</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+          <t>কৃতকাজ $W = 0$, বলরেখাগুলো সর্বদা লম্বভাবে ($90^\circ$ কোণে) ছেদ করে</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4600,38 +4338,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ধারকত্ব, সঞ্চিত শক্তি ও সমান্তরাল পাত ধারক 19</t>
+          <t>তড়িৎ বিভব, কৃতকাজ ও স্থির তড়িৎ শক্তি (Electric Potential &amp; Energy)</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>$5\ \mu\text{F}$ এবং $5\ \mu\text{F}$ ধারকত্বের দুটি ধারককে সমান্তরালে যুক্ত করে $30\text{ V}$ ব্যাটারির সাথে সংযুক্ত করা হলো। বর্তনীর তুল্য ধারকত্ব এবং উভয় ধারকে সঞ্চিত মোট তড়িৎ শক্তি কত?</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
+          <t>##GEO:circle[r=3][size:small]##
+একটি $R = 20\text{ cm}$ ব্যাসার্ধের পাতলা পরিবাহী চাকতিতে সুষম তলমাত্রিক আধান ঘনত্ব $\sigma = 5.0\text{ }\mu	ext{C/m}^2$ রয়েছে। চাকতির অক্ষের ওপর কেন্দ্র হতে $x = 15\text{ cm}$ দূরে তড়িৎ বিভব নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>$C_p = C_1 + C_2 = 5 + 5 = 10\ \mu\text{F}$।
-শক্তি $U = \frac{1}{2} C_p V^2 = 0.5 \times (10 \times 10^{-6}) \times 30^2 = 0.0045\text{ J}$।</t>
+          <t>চাকতির অক্ষীয় বিভব $V = \frac{\sigma}{2\epsilon_0}\left(\sqrt{R^2 + x^2} - x\right)$। $\sqrt{R^2 + x^2} = \sqrt{0.20^2 + 0.15^2} = \sqrt{0.04 + 0.0225} = \sqrt{0.0625} = 0.25\text{ m}$। $\sqrt{R^2+x^2} - x = 0.25 - 0.15 = 0.10\text{ m}$। $V = \frac{5.0 \times 10^{-6}}{2(8.854 \times 10^{-12})} \times 0.10 = \frac{5.0 \times 10^{-7}}{1.7708 \times 10^{-11}} \approx 28235.8\text{ V} \approx 28.24\text{ kV}$।</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>$C_p = 10\ \mu\text{F}, U = 0.0045\text{ J}$</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+          <t>অক্ষীয় বিভব $V = 2.827 \times 10^4\text{ V} \approx 28.27\text{ kV}$</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4651,43 +4389,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ধারকত্ব, সঞ্চিত শক্তি ও সমান্তরাল পাত ধারক 20</t>
+          <t>তড়িৎ বিভব, কৃতকাজ ও স্থির তড়িৎ শক্তি (Electric Potential &amp; Energy)</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>##PRESET:circuit-resistors[size:medium]##
-$6\ \mu\text{F}$ এবং $6\ \mu\text{F}$ ধারকত্বের দুটি ধারককে সমান্তরালে যুক্ত করে $12\text{ V}$ ব্যাটারির সাথে সংযুক্ত করা হলো। বর্তনীর তুল্য ধারকত্ব এবং উভয় ধারকে সঞ্চিত মোট তড়িৎ শক্তি কত?</t>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি ধনাত্মক আধান $Q = 10\text{ nC}$ হতে $r_A = 10\text{ cm}$ দূরে একটি বিন্দু $A$ এবং $r_B = 20\text{ cm}$ দূরে একটি বিন্দু $B$। $B$ হতে $A$-তে একটি ইলেকট্রনকে স্থানান্তরিত করতে বাহ্যিক বল দ্বারা কৃতকাজ কত?</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>##PRESET:circuit-resistors[size:medium]##</t>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>$C_p = C_1 + C_2 = 6 + 6 = 12\ \mu\text{F}$।
-শক্তি $U = \frac{1}{2} C_p V^2 = 0.5 \times (12 \times 10^{-6}) \times 12^2 = 0.00086\text{ J}$।</t>
+          <t>বিভবের মান $V_A = \frac{kQ}{r_A} = \frac{(9 \times 10^9)(10 \times 10^{-9})}{0.10} = 900\text{ V}$। $V_B = \frac{kQ}{r_B} = 450\text{ V}$। বিভব পার্থক্য $V_A - V_B = 900 - 450 = +450\text{ V}$। ইলেকট্রনের আধান $q = -1.6 \times 10^{-19}\text{ C}$। বাহ্যিক কৃতকাজ $W = q(V_A - V_B) = (-1.6 \times 10^{-19}) \times 450 = -7.20 \times 10^{-17}\text{ J}$।</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>$C_p = 12\ \mu\text{F}, U = 0.00086\text{ J}$</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+          <t>কৃতকাজ $W = -7.20 \times 10^{-17}\text{ J}$ (তড়িৎ ক্ষেত্রের বিরুদ্ধে কাজ ঋণাত্মক, ক্ষেত্র দ্বারা সম্পাদিত কাজ ধনাত্মক)</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4707,38 +4440,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>ধারকত্ব, সঞ্চিত শক্তি ও সমান্তরাল পাত ধারক 21</t>
+          <t>ধারকত্ব, ডাই-ইলেকট্রিক ও স্থির তড়িৎ শক্তি (Capacitance &amp; Energy Density)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>$7\ \mu\text{F}$ এবং $7\ \mu\text{F}$ ধারকত্বের দুটি ধারককে সমান্তরালে যুক্ত করে $14\text{ V}$ ব্যাটারির সাথে সংযুক্ত করা হলো। বর্তনীর তুল্য ধারকত্ব এবং উভয় ধারকে সঞ্চিত মোট তড়িৎ শক্তি কত?</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি সমান্তরাল পাত ধারকের প্রতি পাতের ক্ষেত্রফল $A = 0.04\text{ m}^2$ এবং পাতদ্বয়ের মধ্যবর্তী দূরত্ব $d = 2.0\text{ mm}$। বায়ুর উপস্থিতিতে এর ধারকত্ব কত? পাতদ্বয়ের মাঝে $K = 5.0$ ডাই-ইলেকট্রিক ধ্রুবক বিশিষ্ট কাচ প্রবেশ করালে নতুন ধারকত্ব কত হবে? ($\epsilon_0 = 8.854 \times 10^{-12}\text{ F/m}$)।</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>$C_p = C_1 + C_2 = 7 + 7 = 14\ \mu\text{F}$।
-শক্তি $U = \frac{1}{2} C_p V^2 = 0.5 \times (14 \times 10^{-6}) \times 14^2 = 0.00137\text{ J}$।</t>
+          <t>বায়ু মাধ্যমে: $C_0 = \frac{\epsilon_0 A}{d} = \frac{(8.854 \times 10^{-12}) \times 0.04}{2.0 \times 10^{-3}} = \frac{3.5416 \times 10^{-13}}{2 \times 10^{-3}} = 1.7708 \times 10^{-10}\text{ F} = 177.08\text{ pF}$। ডাই-ইলেকট্রিক মাধ্যমে: $C = K C_0 = 5.0 \times 177.08\text{ pF} = 885.4\text{ pF}$।</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>$C_p = 14\ \mu\text{F}, U = 0.00137\text{ J}$</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+          <t>বায়ুতে ধারকত্ব $C_0 = 177.08\text{ pF}$, কাচ মাধ্যমে $C = 885.4\text{ pF}$</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4758,38 +4491,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>ধারকত্ব, সঞ্চিত শক্তি ও সমান্তরাল পাত ধারক 22</t>
+          <t>ধারকত্ব, ডাই-ইলেকট্রিক ও স্থির তড়িৎ শক্তি (Capacitance &amp; Energy Density)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>$8\ \mu\text{F}$ এবং $8\ \mu\text{F}$ ধারকত্বের দুটি ধারককে সমান্তরালে যুক্ত করে $16\text{ V}$ ব্যাটারির সাথে সংযুক্ত করা হলো। বর্তনীর তুল্য ধারকত্ব এবং উভয় ধারকে সঞ্চিত মোট তড়িৎ শক্তি কত?</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি $10\text{ }\mu	ext{F}$ ধারককে $100\text{ V}$ ব্যাটারি দ্বারা পূর্ণ চার্জ করা হলো। এরপর ব্যাটারি বিচ্ছিন্ন করে ধারকটির পাত দুটির দূরত্ব দ্বিগুণ করা হলো। ধারকটির ধারকত্ব, পাতদ্বয়ের বিভব পার্থক্য এবং সঞ্চিত শক্তির পরিবর্তন কী ঘটবে?</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>$C_p = C_1 + C_2 = 8 + 8 = 16\ \mu\text{F}$।
-শক্তি $U = \frac{1}{2} C_p V^2 = 0.5 \times (16 \times 10^{-6}) \times 16^2 = 0.00205\text{ J}$।</t>
+          <t>ব্যাটারি বিচ্ছিন্ন করায় আধান ধ্রুব থাকে: $Q = C V = (10 \times 10^{-6})(100) = 1.0 \times 10^{-3}\text{ C}$। দূরত্ব দ্বিগুণ হলে ধারকত্ব অর্ধেক: $C' = C/2 = 5.0\text{ }\mu\text{F}$। নতুন বিভব $V' = \frac{Q}{C'} = \frac{10^{-3}}{5 \times 10^{-6}} = 200.0\text{ V}$। আদি শক্তি $U = \frac{1}{2} C V^2 = 0.5(10^{-5})(10000) = 0.05\text{ J}$। নতুন শক্তি $U' = \frac{1}{2}\frac{Q^2}{C'} = 2U = 0.10\text{ J}$। বাহ্যিক বলের দ্বারা পাত দুটিকে দূরে টানতে কৃতকাজই এই অতিরিক্ত শক্তিতে রূপান্তরিত হয়।</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>$C_p = 16\ \mu\text{F}, U = 0.00205\text{ J}$</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+          <t>ধারকত্ব অর্ধেক ($5.0\text{ }\mu\text{F}$), বিভব পার্থক্য দ্বিগুণ ($200.0\text{ V}$), সঞ্চিত শক্তি দ্বিগুণ হবে ($0.05\text{ J} \to 0.10\text{ J}$)</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4809,38 +4542,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>ধারকত্ব, সঞ্চিত শক্তি ও সমান্তরাল পাত ধারক 23</t>
+          <t>ধারকত্ব, ডাই-ইলেকট্রিক ও স্থির তড়িৎ শক্তি (Capacitance &amp; Energy Density)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>$9\ \mu\text{F}$ এবং $9\ \mu\text{F}$ ধারকত্বের দুটি ধারককে সমান্তরালে যুক্ত করে $18\text{ V}$ ব্যাটারির সাথে সংযুক্ত করা হলো। বর্তনীর তুল্য ধারকত্ব এবং উভয় ধারকে সঞ্চিত মোট তড়িৎ শক্তি কত?</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##
+একটি সমান্তরাল পাত ধারকের পাতের ব্যবধান $d = 6.0\text{ mm}$। এর ভেতর $t = 4.0\text{ mm}$ পুরু এবং $K = 4.0$ পরাবৈদ্যুতিক ধ্রুবকের একটি স্ল্যাব প্রবেশ করানো হলো। স্ল্যাব প্রবেশ করানোর পর ধারকত্ব প্রারম্ভিক বায়ু ধারকত্বের কত গুণ বৃদ্ধি পাবে?</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>$C_p = C_1 + C_2 = 9 + 9 = 18\ \mu\text{F}$।
-শক্তি $U = \frac{1}{2} C_p V^2 = 0.5 \times (18 \times 10^{-6}) \times 18^2 = 0.00292\text{ J}$।</t>
+          <t>বায়ুতে ধারকত্ব $C_0 = \frac{\epsilon_0 A}{d}$। আংশিক ডাই-ইলেকট্রিক থাকলে: $C = \frac{\epsilon_0 A}{d - t + t/K} = \frac{\epsilon_0 A}{6 - 4 + 4/4} = \frac{\epsilon_0 A}{2 + 1} = \frac{\epsilon_0 A}{3.0\text{ mm}}$। অনুপাত $\frac{C}{C_0} = \frac{d}{d - t + t/K} = \frac{6.0}{3.0} = 2.0$ গুণ (স্ল্যাব ছাড়া $6\text{ mm}$-এর তুলনায় দ্বিগুণ)।</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>$C_p = 18\ \mu\text{F}, U = 0.00292\text{ J}$</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+          <t>নতুন ধারকত্ব পূর্বের $1.714$ গুণ হবে ($71.43\%$ বৃদ্ধি পাবে)</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4860,43 +4593,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>ধারকত্ব, সঞ্চিত শক্তি ও সমান্তরাল পাত ধারক 24</t>
+          <t>ধারকত্ব, ডাই-ইলেকট্রিক ও স্থির তড়িৎ শক্তি (Capacitance &amp; Energy Density)</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>##PRESET:circuit-resistors[size:medium]##
-$2\ \mu\text{F}$ এবং $4\ \mu\text{F}$ ধারকত্বের দুটি ধারককে সমান্তরালে যুক্ত করে $20\text{ V}$ ব্যাটারির সাথে সংযুক্ত করা হলো। বর্তনীর তুল্য ধারকত্ব এবং উভয় ধারকে সঞ্চিত মোট তড়িৎ শক্তি কত?</t>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি পরিবাহী গোলকের ব্যাসার্ধ $R = 9.0\text{ cm}$। গোলকটির ধারকত্ব কত ফ্যারাড? এটিকে $1000\text{ V}$ বিভবে আহিত করলে সঞ্চিত স্থির তড়িৎ শক্তি কত জুল হবে?</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>##PRESET:circuit-resistors[size:medium]##</t>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>$C_p = C_1 + C_2 = 2 + 4 = 6\ \mu\text{F}$।
-শক্তি $U = \frac{1}{2} C_p V^2 = 0.5 \times (6 \times 10^{-6}) \times 20^2 = 0.0012\text{ J}$।</t>
+          <t>বিচ্ছিন্ন গোলকের ধারকত্ব $C = 4\pi\epsilon_0 R = \frac{R}{k} = \frac{0.09\text{ m}}{9.0 \times 10^9} = 1.0 \times 10^{-11}\text{ F} = 10.0\text{ pF}$। সঞ্চিত শক্তি $U = \frac{1}{2} C V^2 = \frac{1}{2}(1.0 \times 10^{-11})(1000)^2 = 0.5 \times 10^{-11} \times 10^6 = 5.0 \times 10^{-6}\text{ J} = 5.0\text{ }\mu\text{J}$।</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>$C_p = 6\ \mu\text{F}, U = 0.0012\text{ J}$</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
+          <t>ধারকত্ব $C = 10.0\text{ pF}$, সঞ্চিত শক্তি $U = 5.0 \times 10^{-6}\text{ J} = 5.0\text{ }\mu\text{J}$</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4916,38 +4644,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>ধারকত্ব, সঞ্চিত শক্তি ও সমান্তরাল পাত ধারক 25</t>
+          <t>ধারকত্ব, ডাই-ইলেকট্রিক ও স্থির তড়িৎ শক্তি (Capacitance &amp; Energy Density)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>$3\ \mu\text{F}$ এবং $5\ \mu\text{F}$ ধারকত্বের দুটি ধারককে সমান্তরালে যুক্ত করে $22\text{ V}$ ব্যাটারির সাথে সংযুক্ত করা হলো। বর্তনীর তুল্য ধারকত্ব এবং উভয় ধারকে সঞ্চিত মোট তড়িৎ শক্তি কত?</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি সমান্তরাল পাত ধারকে তড়িৎ ক্ষেত্র $E = 1.0 \times 10^6\text{ V/m}$। প্রতি ঘনমিটার আয়তনে সঞ্চিত তড়িৎ শক্তি ঘনত্ব (Electrostatic energy density $u_E$) নির্ণয় কর। ($\epsilon_0 = 8.854 \times 10^{-12}\text{ F/m}$)।</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>$C_p = C_1 + C_2 = 3 + 5 = 8\ \mu\text{F}$।
-শক্তি $U = \frac{1}{2} C_p V^2 = 0.5 \times (8 \times 10^{-6}) \times 22^2 = 0.00194\text{ J}$।</t>
+          <t>শক্তি ঘনত্ব $u_E = \frac{1}{2}\epsilon_0 E^2 = \frac{1}{2}(8.854 \times 10^{-12}) \times (1.0 \times 10^6)^2 = 4.427 \times 10^{-12} \times 10^{12} = 4.427\text{ J/m}^3$।</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>$C_p = 8\ \mu\text{F}, U = 0.00194\text{ J}$</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
+          <t>শক্তি ঘনত্ব $u_E = 4.427\text{ J/m}^3$</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4967,38 +4695,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>ধারকত্ব, সঞ্চিত শক্তি ও সমান্তরাল পাত ধারক 26</t>
+          <t>ধারকত্ব, ডাই-ইলেকট্রিক ও স্থির তড়িৎ শক্তি (Capacitance &amp; Energy Density)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>$4\ \mu\text{F}$ এবং $6\ \mu\text{F}$ ধারকত্বের দুটি ধারককে সমান্তরালে যুক্ত করে $24\text{ V}$ ব্যাটারির সাথে সংযুক্ত করা হলো। বর্তনীর তুল্য ধারকত্ব এবং উভয় ধারকে সঞ্চিত মোট তড়িৎ শক্তি কত?</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+তিনটি ধারক $C_1 = 2\text{ }\mu	ext{F}, C_2 = 3\text{ }\mu	ext{F}$ এবং $C_3 = 6\text{ }\mu	ext{F}$। এদের (ক) শ্রেণিতে এবং (খ) সমান্তরালে যুক্ত করলে তুল্য ধারকত্ব কত হবে?</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>$C_p = C_1 + C_2 = 4 + 6 = 10\ \mu\text{F}$।
-শক্তি $U = \frac{1}{2} C_p V^2 = 0.5 \times (10 \times 10^{-6}) \times 24^2 = 0.00288\text{ J}$।</t>
+          <t>(ক) শ্রেণি সমবায়ে: $\frac{1}{C_s} = \frac{1}{C_1} + \frac{1}{C_2} + \frac{1}{C_3} = \frac{1}{2} + \frac{1}{3} + \frac{1}{6} = \frac{3 + 2 + 1}{6} = \frac{6}{6} = 1 \implies C_s = 1.0\text{ }\mu\text{F}$। (খ) সমান্তরাল সমবায়ে: $C_p = C_1 + C_2 + C_3 = 2 + 3 + 6 = 11.0\text{ }\mu\text{F}$।</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>$C_p = 10\ \mu\text{F}, U = 0.00288\text{ J}$</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
+          <t>(ক) শ্রেণি সমবায়ে $C_s = 1.0\text{ }\mu\text{F}$, (খ) সমান্তরাল সমবায়ে $C_p = 11.0\text{ }\mu\text{F}$</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5018,38 +4746,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>ধারকত্ব, সঞ্চিত শক্তি ও সমান্তরাল পাত ধারক 27</t>
+          <t>ধারকত্ব, ডাই-ইলেকট্রিক ও স্থির তড়িৎ শক্তি (Capacitance &amp; Energy Density)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>$5\ \mu\text{F}$ এবং $7\ \mu\text{F}$ ধারকত্বের দুটি ধারককে সমান্তরালে যুক্ত করে $26\text{ V}$ ব্যাটারির সাথে সংযুক্ত করা হলো। বর্তনীর তুল্য ধারকত্ব এবং উভয় ধারকে সঞ্চিত মোট তড়িৎ শক্তি কত?</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+দুটি ধারক $C_1 = 4.0\text{ }\mu	ext{F}$ এবং $C_2 = 6.0\text{ }\mu	ext{F}$-কে শ্রেণিতে যুক্ত করে $100\text{ V}$ উৎসের সাথে সংযোগ দেওয়া হলো। প্রতিটি ধারকের পাতদ্বয়ের বিভব পার্থক্য এবং সঞ্চিত আধান নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>$C_p = C_1 + C_2 = 5 + 7 = 12\ \mu\text{F}$।
-শক্তি $U = \frac{1}{2} C_p V^2 = 0.5 \times (12 \times 10^{-6}) \times 26^2 = 0.00406\text{ J}$।</t>
+          <t>শ্রেণির তুল্য ধারকত্ব $C_s = \frac{C_1 C_2}{C_1 + C_2} = \frac{4 \times 6}{10} = 2.4\text{ }\mu\text{F}$। মোট আধান $Q = C_s V = 2.4\text{ }\mu\text{F} \times 100\text{ V} = 240.0\text{ }\mu\text{C}$। শ্রেণি সংযোগে আধান সমান থাকে। ১ম ধারকের বিভব $V_1 = \frac{Q}{C_1} = \frac{240}{4} = 60.0\text{ V}$। ২য় ধারকের বিভব $V_2 = \frac{Q}{C_2} = \frac{240}{6} = 40.0\text{ V}$।</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>$C_p = 12\ \mu\text{F}, U = 0.00406\text{ J}$</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
+          <t>তুল্য আধান $Q = 240.0\text{ }\mu\text{C}$, $V_1 = 60.0\text{ V}, V_2 = 40.0\text{ V}$</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5069,43 +4797,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>ধারকত্ব, সঞ্চিত শক্তি ও সমান্তরাল পাত ধারক 28</t>
+          <t>ধারকত্ব, ডাই-ইলেকট্রিক ও স্থির তড়িৎ শক্তি (Capacitance &amp; Energy Density)</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>##PRESET:circuit-resistors[size:medium]##
-$6\ \mu\text{F}$ এবং $8\ \mu\text{F}$ ধারকত্বের দুটি ধারককে সমান্তরালে যুক্ত করে $28\text{ V}$ ব্যাটারির সাথে সংযুক্ত করা হলো। বর্তনীর তুল্য ধারকত্ব এবং উভয় ধারকে সঞ্চিত মোট তড়িৎ শক্তি কত?</t>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+একটি $C_1 = 2.0\text{ }\mu	ext{F}$ ধারককে $200\text{ V}$ পর্যন্ত চার্জিত করে ব্যাটারি বিচ্ছিন্ন করা হলো। এরপর এটিকে একটি চার্জহীন $C_2 = 8.0\text{ }\mu	ext{F}$ ধারকের সাথে সমান্তরালে যুক্ত করা হলো। সাধারণ বিভব (Common potential $V_c$) এবং সংযোগের ফলে শক্তির ক্ষয় $\Delta U$ নির্ণয় কর।</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>##PRESET:circuit-resistors[size:medium]##</t>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>$C_p = C_1 + C_2 = 6 + 8 = 14\ \mu\text{F}$।
-শক্তি $U = \frac{1}{2} C_p V^2 = 0.5 \times (14 \times 10^{-6}) \times 28^2 = 0.00549\text{ J}$।</t>
+          <t>সাধারণ বিভব $V_c = \frac{C_1 V_1 + C_2 V_2}{C_1 + C_2} = \frac{(2.0 \times 10^{-6})(200) + 0}{(2.0 + 8.0) \times 10^{-6}} = \frac{400 \times 10^{-6}}{10 \times 10^{-6}} = 40.0\text{ V}$। আদি শক্তি $U_i = \frac{1}{2} C_1 V_1^2 = \frac{1}{2}(2.0 \times 10^{-6})(40000) = 0.040\text{ J}$। অন্তিম শক্তি $U_f = \frac{1}{2}(C_1 + C_2)V_c^2 = \frac{1}{2}(10 \times 10^{-6})(1600) = 0.008\text{ J}$। শক্তি ক্ষয় $\Delta U = 0.040 - 0.008 = 0.032\text{ J} = 32.0\text{ mJ}$ (তারের রোধে তাপ ও বিকিরণে ক্ষয় হয়)।</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>$C_p = 14\ \mu\text{F}, U = 0.00549\text{ J}$</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
+          <t>সাধারণ বিভব $V_c = 40.0\text{ V}$, শক্তির ক্ষয় $\Delta U = 0.032\text{ J} = 32.0\text{ mJ}$</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5125,38 +4848,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>ধারকত্ব, সঞ্চিত শক্তি ও সমান্তরাল পাত ধারক 29</t>
+          <t>ধারকত্ব, ডাই-ইলেকট্রিক ও স্থির তড়িৎ শক্তি (Capacitance &amp; Energy Density)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>$7\ \mu\text{F}$ এবং $9\ \mu\text{F}$ ধারকত্বের দুটি ধারককে সমান্তরালে যুক্ত করে $30\text{ V}$ ব্যাটারির সাথে সংযুক্ত করা হলো। বর্তনীর তুল্য ধারকত্ব এবং উভয় ধারকে সঞ্চিত মোট তড়িৎ শক্তি কত?</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+চিত্রের ধারক নেটওয়ার্কে চারটি সমরূপ পাত পরস্পর হতে $d$ ব্যবধানে সমান্তরালে সাজানো। একান্তর পাতগুলোকে একত্রে তার দ্বারা যুক্ত করা হলে ব্যবস্থার তুল্য ধারকত্ব একটি একক সমান্তরাল পাত ধারকের কত গুণ হবে?</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>$C_p = C_1 + C_2 = 7 + 9 = 16\ \mu\text{F}$।
-শক্তি $U = \frac{1}{2} C_p V^2 = 0.5 \times (16 \times 10^{-6}) \times 30^2 = 0.0072\text{ J}$।</t>
+          <t>$N = 4$টি পাত সমান্তরালে পর্যায়ক্রমে যুক্ত করলে মোট $N - 1 = 3$টি ধারক তৈরি হয় যারা পরস্পরের সাথে সমান্তরাল সমবায়ে যুক্ত। একটি একক ধারকের ধারকত্ব $C_0 = \frac{\epsilon_0 A}{d}$ হলে সমবায়ের মোট তুল্য ধারকত্ব $C_{\text{eq}} = (N - 1)C_0 = 3 C_0$।</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>$C_p = 16\ \mu\text{F}, U = 0.0072\text{ J}$</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
+          <t>তুল্য ধারকত্ব $3.0 C_0$</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5176,38 +4899,38 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ধারকত্ব, সঞ্চিত শক্তি ও সমান্তরাল পাত ধারক 30</t>
+          <t>ধারকত্ব, ডাই-ইলেকট্রিক ও স্থির তড়িৎ শক্তি (Capacitance &amp; Energy Density)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>$8\ \mu\text{F}$ এবং $4\ \mu\text{F}$ ধারকত্বের দুটি ধারককে সমান্তরালে যুক্ত করে $12\text{ V}$ ব্যাটারির সাথে সংযুক্ত করা হলো। বর্তনীর তুল্য ধারকত্ব এবং উভয় ধারকে সঞ্চিত মোট তড়িৎ শক্তি কত?</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি পাত ধারকের পাতদ্বয়ের মধ্যে আকর্ষণ বলের রাশিমালা $F = rac{Q^2}{2\epsilon_0 A} = rac{1}{2}QE$ প্রতিপাদন কর। সূত্রের সামনে $rac{1}{2}$ ফ্যাক্টরটি কেন উপস্থিত ব্যাখ্যা কর।</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>$C_p = C_1 + C_2 = 8 + 4 = 12\ \mu\text{F}$।
-শক্তি $U = \frac{1}{2} C_p V^2 = 0.5 \times (12 \times 10^{-6}) \times 12^2 = 0.00086\text{ J}$।</t>
+          <t>দুই পাতের মাঝে মোট ক্ষেত্র $E = \frac{\sigma}{\epsilon_0} = \frac{Q}{\epsilon_0 A}$। এর অর্ধেক ($E/2$) সৃষ্টি হয় ১ম পাতের আধান দ্বারা এবং বাকি অর্ধেক ($E/2$) ২য় পাতের আধান দ্বারা। নিজের আধান নিজের ওপর বল প্রয়োগ করে না; ফলে ২য় পাতের আধান $Q$-এর ওপর ১ম পাতের কার্যকর ক্ষেত্র কেবল $\frac{E}{2}$। সুতরাং আকর্ষণ বল $F = Q\left(\frac{E}{2}\right) = \frac{1}{2}QE = \frac{Q^2}{2\epsilon_0 A}$।</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>$C_p = 12\ \mu\text{F}, U = 0.00086\text{ J}$</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
+          <t>$F = \frac{1}{2}QE$, কারণ প্রতিটি পাত কেবল অপর পাতের তড়িৎ ক্ষেত্রের ($E/2$) প্রভাব অনুভব করে</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5227,38 +4950,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>ধারকত্ব, সঞ্চিত শক্তি ও সমান্তরাল পাত ধারক 31</t>
+          <t>গাউসের সূত্র ও উন্নত স্থির তড়িৎ জ্যামিতি (Gauss Law &amp; Geometry)</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>$9\ \mu\text{F}$ এবং $5\ \mu\text{F}$ ধারকত্বের দুটি ধারককে সমান্তরালে যুক্ত করে $14\text{ V}$ ব্যাটারির সাথে সংযুক্ত করা হলো। বর্তনীর তুল্য ধারকত্ব এবং উভয় ধারকে সঞ্চিত মোট তড়িৎ শক্তি কত?</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr"/>
+          <t>##GEO:rect[w=3,h=3][size:small]##
+একটি ঘনকের ঠিক কেন্দ্রে $q = +8.854\text{ }\mu	ext{C}$ বিন্দু আধান রাখা আছে। গাউসের সূত্রানুযায়ী ঘনকের সমগ্র পৃষ্ঠের মধ্য দিয়ে অতিক্রান্ত মোট তড়িৎ ফ্লাক্স $\Phi$ কত? ঘনকের যেকোনো একটি তলের মধ্য দিয়ে অতিক্রান্ত ফ্লাক্স $\Phi_1$ কত?</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=3,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>$C_p = C_1 + C_2 = 9 + 5 = 14\ \mu\text{F}$।
-শক্তি $U = \frac{1}{2} C_p V^2 = 0.5 \times (14 \times 10^{-6}) \times 14^2 = 0.00137\text{ J}$।</t>
+          <t>গাউসের সূত্র: মোট ফ্লাক্স $\Phi = \frac{q_{\text{enclosed}}}{\epsilon_0} = \frac{8.854 \times 10^{-6}\text{ C}}{8.854 \times 10^{-12}\text{ C}^2/\text{N}\cdot\text{m}^2} = 1.0 \times 10^6\text{ N}\cdot\text{m}^2/\text{C}$। ঘনকের ৬টি তল সম্পূর্ণ প্রতিসম হওয়ায় যেকোনো একটি তলের মধ্য দিয়ে অতিক্রান্ত ফ্লাক্স $\Phi_1 = \frac{\Phi}{6} = \frac{1.0 \times 10^6}{6} \approx 1.667 \times 10^5\text{ N}\cdot\text{m}^2/\text{C}$।</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>$C_p = 14\ \mu\text{F}, U = 0.00137\text{ J}$</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+          <t>মোট ফ্লাক্স $\Phi = 1.0 \times 10^6\text{ N}\cdot\text{m}^2/\text{C}$, প্রতিটি তলে $\Phi_1 = 1.667 \times 10^5\text{ N}\cdot\text{m}^2/\text{C}$</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5278,43 +5001,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>ধারকত্ব, সঞ্চিত শক্তি ও সমান্তরাল পাত ধারক 32</t>
+          <t>গাউসের সূত্র ও উন্নত স্থির তড়িৎ জ্যামিতি (Gauss Law &amp; Geometry)</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>##PRESET:circuit-resistors[size:medium]##
-$2\ \mu\text{F}$ এবং $6\ \mu\text{F}$ ধারকত্বের দুটি ধারককে সমান্তরালে যুক্ত করে $16\text{ V}$ ব্যাটারির সাথে সংযুক্ত করা হলো। বর্তনীর তুল্য ধারকত্ব এবং উভয় ধারকে সঞ্চিত মোট তড়িৎ শক্তি কত?</t>
+          <t>##GEO:rect[w=3,h=3][size:small]##
+একটি ঘনকের একটি শীর্ষবিন্দুতে (Corner of a cube) একটি বিন্দু আধান $q$ স্থাপন করা হলো। ঘনকটির সমগ্র পৃষ্ঠের মধ্য দিয়ে অতিক্রান্ত মোট ফ্লাক্স কত হবে?</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>##PRESET:circuit-resistors[size:medium]##</t>
+          <t>##GEO:rect[w=3,h=3][size:small]##</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>$C_p = C_1 + C_2 = 2 + 6 = 8\ \mu\text{F}$।
-শক্তি $U = \frac{1}{2} C_p V^2 = 0.5 \times (8 \times 10^{-6}) \times 16^2 = 0.00102\text{ J}$।</t>
+          <t>শীর্ষবিন্দুতে অবস্থিত আধানকে সম্পূর্ণ ঘিরে রাখতে মোট ৮টি ঘনক প্রয়োজন হয়। ফলে ৮টি ঘনকের মধ্য দিয়ে মোট ফ্লাক্স $\frac{q}{\epsilon_0}$। প্রতিসমতার কারণে নির্দিষ্ট একটি ঘনকের মধ্য দিয়ে অতিক্রান্ত ফ্লাক্স মোট ফ্লাক্সের $\frac{1}{8}$ অংশ, অর্থাৎ $\Phi = \frac{q}{8\epsilon_0}$।</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>$C_p = 8\ \mu\text{F}, U = 0.00102\text{ J}$</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+          <t>মোট ফ্লাক্স $\Phi = \frac{q}{8\epsilon_0}$</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5334,38 +5052,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>ধারকত্ব, সঞ্চিত শক্তি ও সমান্তরাল পাত ধারক 33</t>
+          <t>গাউসের সূত্র ও উন্নত স্থির তড়িৎ জ্যামিতি (Gauss Law &amp; Geometry)</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>$3\ \mu\text{F}$ এবং $7\ \mu\text{F}$ ধারকত্বের দুটি ধারককে সমান্তরালে যুক্ত করে $18\text{ V}$ ব্যাটারির সাথে সংযুক্ত করা হলো। বর্তনীর তুল্য ধারকত্ব এবং উভয় ধারকে সঞ্চিত মোট তড়িৎ শক্তি কত?</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr"/>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##
+একটি অসীম দীর্ঘ সোজা তারের রৈখিক আধান ঘনত্ব $\lambda = 2.0 \times 10^{-6}\text{ C/m}$। তার হতে লম্ব দূরত্ব $r = 10\text{ cm}$ বিন্দুতে তড়িৎ প্রাবল্যের মান নির্ণয় কর। ($\epsilon_0 = 8.854 \times 10^{-12}\text{ F/m}$)।</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>$C_p = C_1 + C_2 = 3 + 7 = 10\ \mu\text{F}$।
-শক্তি $U = \frac{1}{2} C_p V^2 = 0.5 \times (10 \times 10^{-6}) \times 18^2 = 0.00162\text{ J}$।</t>
+          <t>গাউসের সূত্রানুযায়ী অসীম তারের জন্য প্রাবল্য $E = \frac{\lambda}{2\pi\epsilon_0 r} = \frac{2k\lambda}{r} = \frac{2(9.0 \times 10^9) \times (2.0 \times 10^{-6})}{0.10} = \frac{36000}{0.10} = 3.60 \times 10^5\text{ N/C}$।</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>$C_p = 10\ \mu\text{F}, U = 0.00162\text{ J}$</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
+          <t>তড়িৎ প্রাবল্য $E = 3.60 \times 10^5\text{ N/C}$</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5385,38 +5103,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>ধারকত্ব, সঞ্চিত শক্তি ও সমান্তরাল পাত ধারক 34</t>
+          <t>গাউসের সূত্র ও উন্নত স্থির তড়িৎ জ্যামিতি (Gauss Law &amp; Geometry)</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>$4\ \mu\text{F}$ এবং $8\ \mu\text{F}$ ধারকত্বের দুটি ধারককে সমান্তরালে যুক্ত করে $20\text{ V}$ ব্যাটারির সাথে সংযুক্ত করা হলো। বর্তনীর তুল্য ধারকত্ব এবং উভয় ধারকে সঞ্চিত মোট তড়িৎ শক্তি কত?</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+একটি অসীম বিস্তৃত পাতলা কুপরিবাহী সমতল পাতের তলমাত্রিক আধান ঘনত্ব $\sigma = 8.854 \times 10^{-8}\text{ C/m}^2$। পাতের নিকটবর্তী যেকোনো বিন্দুতে তড়িৎ প্রাবল্য কত এবং তা কি পাতের দূরত্বের ওপর নির্ভরশীল?</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>$C_p = C_1 + C_2 = 4 + 8 = 12\ \mu\text{F}$।
-শক্তি $U = \frac{1}{2} C_p V^2 = 0.5 \times (12 \times 10^{-6}) \times 20^2 = 0.0024\text{ J}$।</t>
+          <t>পাতলা চাদরের জন্য গাউসের সূত্রানুযায়ী $E = \frac{\sigma}{2\epsilon_0} = \frac{8.854 \times 10^{-8}}{2(8.854 \times 10^{-12})} = \frac{10^4}{2} = 5000.0\text{ N/C}$। এই সমীকরণে দূরত্ব $r$ অনুপস্থিত থাকায় পাতের নিকটবর্তী অঞ্চলে তড়িৎ ক্ষেত্র সম্পূর্ণ সুষম এবং দূরত্ব নিরপেক্ষ।</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>$C_p = 12\ \mu\text{F}, U = 0.0024\text{ J}$</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
+          <t>তড়িৎ প্রাবল্য $E = 5000.0\text{ N/C}$ (দূরত্বের ওপর সম্পূর্ণ স্বাধীন/অনির্ভরশীল)</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5436,38 +5154,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>ধারকত্ব, সঞ্চিত শক্তি ও সমান্তরাল পাত ধারক 35</t>
+          <t>গাউসের সূত্র ও উন্নত স্থির তড়িৎ জ্যামিতি (Gauss Law &amp; Geometry)</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>$5\ \mu\text{F}$ এবং $9\ \mu\text{F}$ ধারকত্বের দুটি ধারককে সমান্তরালে যুক্ত করে $22\text{ V}$ ব্যাটারির সাথে সংযুক্ত করা হলো। বর্তনীর তুল্য ধারকত্ব এবং উভয় ধারকে সঞ্চিত মোট তড়িৎ শক্তি কত?</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি পরিবাহী গোলকের আধান ঘনত্ব $\sigma$। প্রমাণ কর যে পরিবাহীর বহিঃপৃষ্ঠের ঠিক সন্নিকটে প্রাবল্য $E = rac{\sigma}{\epsilon_0}$ এবং এটি পরিবাহীর পৃষ্ঠে প্রতি একক ক্ষেত্রফলে $rac{\sigma^2}{2\epsilon_0}$ পরিমাণ বহির্মুখী স্থির তড়িৎ চাপ (Electrostatic pressure) সৃষ্টি করে।</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>$C_p = C_1 + C_2 = 5 + 9 = 14\ \mu\text{F}$।
-শক্তি $U = \frac{1}{2} C_p V^2 = 0.5 \times (14 \times 10^{-6}) \times 22^2 = 0.00339\text{ J}$।</t>
+          <t>পরিবাহীর অভ্যন্তরে ক্ষেত্র শূন্য হওয়ায় গাউসীয় চোঙের কেবল বাইরের তল দিয়ে ফ্লাক্স নির্গত হয়: $E \Delta A = \frac{\sigma \Delta A}{\epsilon_0} \implies E = \frac{\sigma}{\epsilon_0}$। পৃষ্ঠের ক্ষুদ্র ক্ষেত্রফল $\Delta A$-এর আধান $\sigma \Delta A$-এর ওপর অবশিষ্ট পরিবাহীর নিজস্ব ক্ষেত্র $\frac{E}{2} = \frac{\sigma}{2\epsilon_0}$ বল প্রয়োগ করে: $\Delta F = (\sigma \Delta A)\left(\frac{\sigma}{2\epsilon_0}\right)$। চাপ $P = \frac{\Delta F}{\Delta A} = \frac{\sigma^2}{2\epsilon_0} = \frac{1}{2}\epsilon_0 E^2$।</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>$C_p = 14\ \mu\text{F}, U = 0.00339\text{ J}$</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+          <t>$E = \frac{\sigma}{\epsilon_0}$, স্থির তড়িৎ চাপ $P = \frac{\sigma^2}{2\epsilon_0} = \frac{1}{2}\epsilon_0 E^2$</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5487,43 +5205,38 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>ধারকত্ব, সঞ্চিত শক্তি ও সমান্তরাল পাত ধারক 36</t>
+          <t>গাউসের সূত্র ও উন্নত স্থির তড়িৎ জ্যামিতি (Gauss Law &amp; Geometry)</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>##PRESET:circuit-resistors[size:medium]##
-$6\ \mu\text{F}$ এবং $4\ \mu\text{F}$ ধারকত্বের দুটি ধারককে সমান্তরালে যুক্ত করে $24\text{ V}$ ব্যাটারির সাথে সংযুক্ত করা হলো। বর্তনীর তুল্য ধারকত্ব এবং উভয় ধারকে সঞ্চিত মোট তড়িৎ শক্তি কত?</t>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি সাবান বুদবুদের ব্যাসার্ধ $R = 2.0\text{ cm}$ এবং পানির পৃষ্ঠটান $T = 0.03\text{ N/m}$। বুদবুদটিকে সর্বোচ্চ কত বিভবে আহিত করলে অতিরিক্ত তড়িৎ চাপের প্রভাবে এটি ফেটে যাবে? (বায়ুমণ্ডলীয় চাপ প্রভাবহীন ধরে)।</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>##PRESET:circuit-resistors[size:medium]##</t>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>$C_p = C_1 + C_2 = 6 + 4 = 10\ \mu\text{F}$।
-শক্তি $U = \frac{1}{2} C_p V^2 = 0.5 \times (10 \times 10^{-6}) \times 24^2 = 0.00288\text{ J}$।</t>
+          <t>পৃষ্ঠটানের অন্তঃমুখী চাপ $P_s = \frac{4T}{R} = \frac{4(0.03)}{0.02} = 6.0\text{ N/m}^2$। স্থির তড়িৎ বহির্মুখী চাপ $P_e = \frac{1}{2}\epsilon_0 E^2 = P_s \implies E^2 = \frac{2 P_s}{\epsilon_0} = \frac{2(6.0)}{8.854 \times 10^{-12}} = 1.355 \times 10^{12} \implies E = 1.164 \times 10^6\text{ V/m}$। গোলকের বিভব $V = E R = (1.164 \times 10^6)(0.02) \approx 23280\text{ V} \approx 23.3\text{ kV}$।</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>$C_p = 10\ \mu\text{F}, U = 0.00288\text{ J}$</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
+          <t>সর্বোচ্চ বিভব $V \approx 20.8\text{ kV}$</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5543,38 +5256,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>ধারকত্ব, সঞ্চিত শক্তি ও সমান্তরাল পাত ধারক 37</t>
+          <t>গাউসের সূত্র ও উন্নত স্থির তড়িৎ জ্যামিতি (Gauss Law &amp; Geometry)</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>$7\ \mu\text{F}$ এবং $5\ \mu\text{F}$ ধারকত্বের দুটি ধারককে সমান্তরালে যুক্ত করে $26\text{ V}$ ব্যাটারির সাথে সংযুক্ত করা হলো। বর্তনীর তুল্য ধারকত্ব এবং উভয় ধারকে সঞ্চিত মোট তড়িৎ শক্তি কত?</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr"/>
+          <t>##GEO:circle[r=3][size:small]##
+দুটি কেন্দ্রীক ফাঁপা পরিবাহী গোলকের ব্যাসার্ধ যথাক্রমে $a = 5.0\text{ cm}$ এবং $b = 10.0\text{ cm}$। অন্তর্বর্তী গোলকে $+Q = 2.0\text{ }\mu	ext{C}$ আধান দেওয়া হলো এবং বহিস্থ গোলকটি ভূ-সংযুক্ত (Grounded)। এই গোলীয় ধারকের ধারকত্ব কত?</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>$C_p = C_1 + C_2 = 7 + 5 = 12\ \mu\text{F}$।
-শক্তি $U = \frac{1}{2} C_p V^2 = 0.5 \times (12 \times 10^{-6}) \times 26^2 = 0.00406\text{ J}$।</t>
+          <t>গোলীয় ধারকের ধারকত্ব $C = 4\pi\epsilon_0 \frac{ab}{b - a} = \frac{1}{k}\frac{ab}{b - a} = \frac{1}{9 \times 10^9}\frac{(0.05)(0.10)}{0.10 - 0.05} = \frac{0.005}{(9 \times 10^9)(0.05)} = \frac{0.10}{9 \times 10^9} = 1.111 \times 10^{-11}\text{ F} \approx 11.12\text{ pF}$। বিভব $V = \frac{Q}{C} = \frac{2 \times 10^{-6}}{1.111 \times 10^{-11}} = 1.80 \times 10^5\text{ V}$।</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>$C_p = 12\ \mu\text{F}, U = 0.00406\text{ J}$</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
+          <t>ধারকত্ব $C = 11.12\text{ pF}$, অভ্যন্তরীণ গোলকের বিভব $V = 1.80 \times 10^5\text{ V}$</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5594,38 +5307,38 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>ধারকত্ব, সঞ্চিত শক্তি ও সমান্তরাল পাত ধারক 38</t>
+          <t>গাউসের সূত্র ও উন্নত স্থির তড়িৎ জ্যামিতি (Gauss Law &amp; Geometry)</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>$8\ \mu\text{F}$ এবং $6\ \mu\text{F}$ ধারকত্বের দুটি ধারককে সমান্তরালে যুক্ত করে $28\text{ V}$ ব্যাটারির সাথে সংযুক্ত করা হলো। বর্তনীর তুল্য ধারকত্ব এবং উভয় ধারকে সঞ্চিত মোট তড়িৎ শক্তি কত?</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=4][size:small]##
+একটি সিলিন্ডারাকার ধারকের অন্তর্ব্যাসার্ধ $a = 1.0\text{ cm}$, বহির্ব্যাসার্ধ $b = 2.718\text{ cm}$ এবং দৈর্ঘ্য $L = 1.0\text{ m}$। ধারকটির একক দৈর্ঘ্যের ধারকত্ব নির্ণয় কর। ($\epsilon_0 = 8.854 \times 10^{-12}\text{ F/m}$)।</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>$C_p = C_1 + C_2 = 8 + 6 = 14\ \mu\text{F}$।
-শক্তি $U = \frac{1}{2} C_p V^2 = 0.5 \times (14 \times 10^{-6}) \times 28^2 = 0.00549\text{ J}$।</t>
+          <t>সিলিন্ডারাকার ধারকের ধারকত্ব $C = \frac{2\pi\epsilon_0 L}{\ln(b/a)}$। এখানে $\frac{b}{a} = \frac{2.718}{1.0} \approx e \implies \ln(b/a) = \ln(e) = 1.0$। অতএব $C = 2\pi\epsilon_0 L = 2 \times 3.1416 \times (8.854 \times 10^{-12}) \times 1.0 \approx 5.563 \times 10^{-11}\text{ F} = 55.63\text{ pF}$।</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>$C_p = 14\ \mu\text{F}, U = 0.00549\text{ J}$</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
+          <t>ধারকত্ব $C = 55.63\text{ pF}$</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5645,38 +5358,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>ধারকত্ব, সঞ্চিত শক্তি ও সমান্তরাল পাত ধারক 39</t>
+          <t>গাউসের সূত্র ও উন্নত স্থির তড়িৎ জ্যামিতি (Gauss Law &amp; Geometry)</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>$9\ \mu\text{F}$ এবং $7\ \mu\text{F}$ ধারকত্বের দুটি ধারককে সমান্তরালে যুক্ত করে $30\text{ V}$ ব্যাটারির সাথে সংযুক্ত করা হলো। বর্তনীর তুল্য ধারকত্ব এবং উভয় ধারকে সঞ্চিত মোট তড়িৎ শক্তি কত?</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr"/>
+          <t>##GEO:rect[w=3,h=3][size:small]##
+একটি তড়িৎ ক্ষেত্রে প্রাবল্য $ec{E} = (3\hat{i} + 4\hat{j} + 5\hat{k})	ext{ N/C}$। $yz$-তলে অবস্থিত $A = 0.20\text{ m}^2$ ক্ষেত্রফলের মধ্য দিয়ে অতিক্রান্ত মোট তড়িৎ ফ্লাক্স $\Phi$ কত?</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=3,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>$C_p = C_1 + C_2 = 9 + 7 = 16\ \mu\text{F}$।
-শক্তি $U = \frac{1}{2} C_p V^2 = 0.5 \times (16 \times 10^{-6}) \times 30^2 = 0.0072\text{ J}$।</t>
+          <t>$yz$-তলের ক্ষেত্রফল ভেক্টর $x$-অক্ষ বরাবর: $\vec{A} = 0.20\hat{i}\text{ m}^2$। ফ্লাক্স $\Phi = \vec{E}\cdot\vec{A} = (3\hat{i} + 4\hat{j} + 5\hat{k})\cdot(0.20\hat{i}) = 3 \times 0.20 = 0.60\text{ N}\cdot\text{m}^2/\text{C}$।</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>$C_p = 16\ \mu\text{F}, U = 0.0072\text{ J}$</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
+          <t>তড়িৎ ফ্লাক্স $\Phi = 0.60\text{ N}\cdot\text{m}^2/\text{C}$</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5696,43 +5409,38 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>ধারকত্ব, সঞ্চিত শক্তি ও সমান্তরাল পাত ধারক 40</t>
+          <t>গাউসের সূত্র ও উন্নত স্থির তড়িৎ জ্যামিতি (Gauss Law &amp; Geometry)</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>##PRESET:circuit-resistors[size:medium]##
-$2\ \mu\text{F}$ এবং $8\ \mu\text{F}$ ধারকত্বের দুটি ধারককে সমান্তরালে যুক্ত করে $12\text{ V}$ ব্যাটারির সাথে সংযুক্ত করা হলো। বর্তনীর তুল্য ধারকত্ব এবং উভয় ধারকে সঞ্চিত মোট তড়িৎ শক্তি কত?</t>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+দুটি সমান্তরাল অসীম পাতের প্রতিটিতে যথাক্রমে $+\sigma$ এবং $-\sigma$ তলমাত্রিক আধান রয়েছে। পাতদ্বয়ের (ক) মধ্যবর্তী স্থানে এবং (খ) বহিস্থ অঞ্চলে তড়িৎ প্রাবল্য কত?</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>##PRESET:circuit-resistors[size:medium]##</t>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>$C_p = C_1 + C_2 = 2 + 8 = 10\ \mu\text{F}$।
-শক্তি $U = \frac{1}{2} C_p V^2 = 0.5 \times (10 \times 10^{-6}) \times 12^2 = 0.00072\text{ J}$।</t>
+          <t>পাতদ্বয়ের অভ্যন্তরে উভয় পাতের প্রাবল্য একই দিকে (ধনাত্মক হতে ঋণাত্মক পাতের দিকে) যোগ হয়: $E = \frac{\sigma}{2\epsilon_0} + \frac{\sigma}{2\epsilon_0} = \frac{\sigma}{\epsilon_0}$। বাইরে উভয় পাতের প্রাবল্য বিপরীতমুখী হওয়ায় পরস্পরকে নাকচ করে: $E = \frac{\sigma}{2\epsilon_0} - \frac{\sigma}{2\epsilon_0} = 0$।</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>$C_p = 10\ \mu\text{F}, U = 0.00072\text{ J}$</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
+          <t>(ক) অভ্যন্তরে $E = \frac{\sigma}{\epsilon_0}$, (খ) বাইরে $E = 0$</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5752,38 +5460,38 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>ধারকত্ব, সঞ্চিত শক্তি ও সমান্তরাল পাত ধারক 41</t>
+          <t>উন্নত স্থির তড়িৎ বিশ্লেষণ ও সমস্যাবলি (Advanced Electrostatics Synthesis)</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>$3\ \mu\text{F}$ এবং $9\ \mu\text{F}$ ধারকত্বের দুটি ধারককে সমান্তরালে যুক্ত করে $14\text{ V}$ ব্যাটারির সাথে সংযুক্ত করা হলো। বর্তনীর তুল্য ধারকত্ব এবং উভয় ধারকে সঞ্চিত মোট তড়িৎ শক্তি কত?</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি ইলেকট্রন $v_0 = 2.0 \times 10^7\text{ m/s}$ আনুভূমিক বেগে দুটি $L = 10\text{ cm}$ দীর্ঘ অনুভূমিক সমান্তরাল পাতের মাঝে প্রবেশ করল। পাতদ্বয়ের প্রাবল্য $E = 1.0 \times 10^4\text{ V/m}$ খাড়া নিচের দিকে ক্রিয়াশীল। পাত অতিক্রম করার মুহূর্তে ইলেকট্রনটির উল্লম্ব বিচ্যুতি $y$ এবং নির্গমন কোণ $\theta$ কত?</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>$C_p = C_1 + C_2 = 3 + 9 = 12\ \mu\text{F}$।
-শক্তি $U = \frac{1}{2} C_p V^2 = 0.5 \times (12 \times 10^{-6}) \times 14^2 = 0.00118\text{ J}$।</t>
+          <t>পাত অতিক্রমে সময় $t = \frac{L}{v_0} = \frac{0.10}{2.0 \times 10^7} = 5.0 \times 10^{-9}\text{ s}$। উল্লম্ব ত্বরণ $a_y = \frac{eE}{m} = \frac{(1.6 \times 10^{-19})(10^4)}{9.11 \times 10^{-31}} \approx 1.7563 \times 10^{15}\text{ m/s}^2$। বিচ্যুতি $y = \frac{1}{2} a_y t^2 = 0.5(1.7563 \times 10^{15})(2.5 \times 10^{-17}) = 0.02195\text{ m} \approx 2.196\text{ cm}$। উল্লম্ব বেগ $v_y = a_y t = (1.7563 \times 10^{15})(5 \times 10^{-9}) = 8.78 \times 10^6\text{ m/s}$। কোণ $\tan\theta = \frac{v_y}{v_0} = \frac{8.78 \times 10^6}{2.0 \times 10^7} = 0.439 \implies \theta \approx 23.71^\circ$।</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>$C_p = 12\ \mu\text{F}, U = 0.00118\text{ J}$</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
+          <t>উল্লম্ব বিচ্যুতি $y = 2.196\text{ cm}$, নির্গমন কোণ $\theta = 23.71^\circ$</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5803,38 +5511,38 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>ধারকত্ব, সঞ্চিত শক্তি ও সমান্তরাল পাত ধারক 42</t>
+          <t>উন্নত স্থির তড়িৎ বিশ্লেষণ ও সমস্যাবলি (Advanced Electrostatics Synthesis)</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>$4\ \mu\text{F}$ এবং $4\ \mu\text{F}$ ধারকত্বের দুটি ধারককে সমান্তরালে যুক্ত করে $16\text{ V}$ ব্যাটারির সাথে সংযুক্ত করা হলো। বর্তনীর তুল্য ধারকত্ব এবং উভয় ধারকে সঞ্চিত মোট তড়িৎ শক্তি কত?</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি ধাতব তারের বলয়ের (Ring) ব্যাসার্ধ $R = 10\text{ cm}$ এবং এতে মোট আধান $Q = +5.0\text{ }\mu	ext{C}$ সুষমভাবে বণ্টিত। বলয়ের অক্ষের ওপর কেন্দ্র হতে কত দূরত্বে তড়িৎ প্রাবল্য সর্বোচ্চ হবে এবং সর্বোচ্চ প্রাবল্যের মান কত?</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>$C_p = C_1 + C_2 = 4 + 4 = 8\ \mu\text{F}$।
-শক্তি $U = \frac{1}{2} C_p V^2 = 0.5 \times (8 \times 10^{-6}) \times 16^2 = 0.00102\text{ J}$।</t>
+          <t>অক্ষীয় প্রাবল্য $E = \frac{k Q x}{(x^2 + R^2)^{3/2}}$। $\frac{dE}{dx} = 0$ করলে সর্বোচ্চ প্রাবল্যের শর্ত পাওয়া যায় $x = \frac{R}{\sqrt{2}} = \frac{0.10}{\sqrt{2}} \approx 0.07071\text{ m} = 7.07\text{ cm}$। মান বসিয়ে: $E_{\max} = \frac{k Q (R/\sqrt{2})}{(3/2 R^2)^{3/2}} = \frac{k Q}{\sqrt{3/2}^3 R^2} \frac{1}{\sqrt{2}} = \frac{2 k Q}{3\sqrt{3} R^2} = \frac{2(9 \times 10^9)(5 \times 10^{-6})}{3\sqrt{3}(0.01)} = \frac{90000}{0.05196} \approx 1.732 \times 10^6\text{ N/C}$।</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>$C_p = 8\ \mu\text{F}, U = 0.00102\text{ J}$</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
+          <t>দূরত্ব $x = \frac{R}{\sqrt{2}} = 7.07\text{ cm}$, সর্বোচ্চ প্রাবল্য $E_{\max} = 1.73 \times 10^6\text{ N/C}$</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5854,38 +5562,38 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>ধারকত্ব, সঞ্চিত শক্তি ও সমান্তরাল পাত ধারক 43</t>
+          <t>উন্নত স্থির তড়িৎ বিশ্লেষণ ও সমস্যাবলি (Advanced Electrostatics Synthesis)</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>$5\ \mu\text{F}$ এবং $5\ \mu\text{F}$ ধারকত্বের দুটি ধারককে সমান্তরালে যুক্ত করে $18\text{ V}$ ব্যাটারির সাথে সংযুক্ত করা হলো। বর্তনীর তুল্য ধারকত্ব এবং উভয় ধারকে সঞ্চিত মোট তড়িৎ শক্তি কত?</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি অর্ধবৃত্তাকার সরু তারের ব্যাসার্ধ $R$ এবং এতে মোট আধান $Q$ সুষমভাবে বণ্টিত। বৃত্তের কেন্দ্রবিন্দুতে তড়িৎ প্রাবল্যের মান কত?</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>$C_p = C_1 + C_2 = 5 + 5 = 10\ \mu\text{F}$।
-শক্তি $U = \frac{1}{2} C_p V^2 = 0.5 \times (10 \times 10^{-6}) \times 18^2 = 0.00162\text{ J}$।</t>
+          <t>রৈখিক আধান ঘনত্ব $\lambda = \frac{Q}{\pi R}$। ক্ষুদ্রাংশ $d\theta$-এর আধান $dq = \lambda R d\theta$। প্রতিসমতার কারণে সমান্তরাল উপাংশ বাতিল হয়ে কেবল লম্ব উপাংশ যোগ হয়: $E = \int_{-\pi/2}^{\pi/2} \frac{k dq}{R^2}\cos\theta = \frac{k\lambda}{R}\int_{-\pi/2}^{\pi/2}\cos\theta d\theta = \frac{k\lambda}{R}(2) = \frac{2k(Q/\pi R)}{R} = \frac{2kQ}{\pi R^2}$।</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>$C_p = 10\ \mu\text{F}, U = 0.00162\text{ J}$</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
+          <t>$E = \frac{2 k Q}{\pi R^2} = \frac{Q}{2\pi^2\epsilon_0 R^2}$</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5905,43 +5613,38 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>ধারকত্ব, সঞ্চিত শক্তি ও সমান্তরাল পাত ধারক 44</t>
+          <t>উন্নত স্থির তড়িৎ বিশ্লেষণ ও সমস্যাবলি (Advanced Electrostatics Synthesis)</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>##PRESET:circuit-resistors[size:medium]##
-$6\ \mu\text{F}$ এবং $6\ \mu\text{F}$ ধারকত্বের দুটি ধারককে সমান্তরালে যুক্ত করে $20\text{ V}$ ব্যাটারির সাথে সংযুক্ত করা হলো। বর্তনীর তুল্য ধারকত্ব এবং উভয় ধারকে সঞ্চিত মোট তড়িৎ শক্তি কত?</t>
+          <t>##GEO:circle[r=3][size:small]##
+একটি $10\text{ cm}$ ব্যাসার্ধের পাতলা পরিবাহী গোলীয় খোলসে $Q_1 = +4.0\text{ }\mu	ext{C}$ আধান আছে। এর কেন্দ্রে একটি বিন্দু আধান $q = +2.0\text{ }\mu	ext{C}$ স্থাপন করা হলো। খোলসের (ক) অন্তর্গাত্রে, (খ) বহির্গাত্রে আধানের পরিমাণ কত হবে এবং কেন্দ্র হতে $20\text{ cm}$ দূরে প্রাবল্য কত?</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>##PRESET:circuit-resistors[size:medium]##</t>
+          <t>##GEO:circle[r=3][size:small]##</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>$C_p = C_1 + C_2 = 6 + 6 = 12\ \mu\text{F}$।
-শক্তি $U = \frac{1}{2} C_p V^2 = 0.5 \times (12 \times 10^{-6}) \times 20^2 = 0.0024\text{ J}$।</t>
+          <t>তড়িৎ আবেশের ফলে খোলসের অভ্যন্তরীণ পৃষ্ঠে সমান ও বিপরীত আধান আবিষ্ট হয়: $q_{\text{in}} = -q = -2.0\text{ }\mu\text{C}$। আধান সংরক্ষণে বহিঃপৃষ্ঠে অতিরিক্ত আধান যোগ হয়ে $Q_{\text{out}} = Q_1 + q = 4.0 + 2.0 = +6.0\text{ }\mu\text{C}$ হয়। কেন্দ্র হতে বাইরে $r = 20\text{ cm}$-এ মোট আবদ্ধ আধান $+6.0\text{ }\mu\text{C}$, ফলে $E = \frac{k(6.0 \times 10^{-6})}{(0.20)^2} = \frac{54000}{0.04} = 1.35 \times 10^6\text{ N/C}$।</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>$C_p = 12\ \mu\text{F}, U = 0.0024\text{ J}$</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
+          <t>(ক) অন্তর্গাত্রে আধান $-2.0\text{ }\mu\text{C}$, (খ) বহির্গাত্রে $+6.0\text{ }\mu\text{C}$, প্রাবল্য $E = 1.35 \times 10^6\text{ N/C}$</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5961,38 +5664,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>ধারকত্ব, সঞ্চিত শক্তি ও সমান্তরাল পাত ধারক 45</t>
+          <t>উন্নত স্থির তড়িৎ বিশ্লেষণ ও সমস্যাবলি (Advanced Electrostatics Synthesis)</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>$7\ \mu\text{F}$ এবং $7\ \mu\text{F}$ ধারকত্বের দুটি ধারককে সমান্তরালে যুক্ত করে $22\text{ V}$ ব্যাটারির সাথে সংযুক্ত করা হলো। বর্তনীর তুল্য ধারকত্ব এবং উভয় ধারকে সঞ্চিত মোট তড়িৎ শক্তি কত?</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr"/>
+          <t>##GEO:rect[w=5,h=2][size:small]##
+একটি অসীম ধারক ল্যাডার নেটওয়ার্কে প্রতিটি ধারক $C = 1.0\text{ }\mu	ext{F}$। চিত্রের ন্যায় শ্রেণি ও সমান্তরালে অসীম পর্যন্ত যুক্ত নেটওয়ার্কটির ইনপুট প্রান্ত $A$ ও $B$-এর তুল্য ধারকত্ব $C_{AB}$ নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=5,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>$C_p = C_1 + C_2 = 7 + 7 = 14\ \mu\text{F}$।
-শক্তি $U = \frac{1}{2} C_p V^2 = 0.5 \times (14 \times 10^{-6}) \times 22^2 = 0.00339\text{ J}$।</t>
+          <t>অসীম ল্যাডারে একটি ধাপ বাদ দিলেও তুল্য ধারকত্ব $C_{AB} = X$ অপরিবর্তিত থাকে। নেটওয়ার্ক সমীকরণ: $X = \frac{C X}{C + X} + \dots$ (যদি সমান্তরাল আগে থাকে) অথবা শ্রেণিতে থাকলে $\frac{1}{X} = \frac{1}{C} + \frac{1}{C + X} \implies X^2 + CX - C^2 = 0 \implies X = \frac{-C + \sqrt{C^2 + 4C^2}}{2} = \frac{\sqrt{5}-1}{2}C \approx 0.618\text{ }\mu\text{F}$।</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>$C_p = 14\ \mu\text{F}, U = 0.00339\text{ J}$</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
+          <t>তুল্য ধারকত্ব $C_{AB} = \frac{\sqrt{5} - 1}{2} C \approx 0.618\text{ }\mu\text{F}$</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6012,38 +5715,38 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>ধারকত্ব, সঞ্চিত শক্তি ও সমান্তরাল পাত ধারক 46</t>
+          <t>উন্নত স্থির তড়িৎ বিশ্লেষণ ও সমস্যাবলি (Advanced Electrostatics Synthesis)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>$8\ \mu\text{F}$ এবং $8\ \mu\text{F}$ ধারকত্বের দুটি ধারককে সমান্তরালে যুক্ত করে $24\text{ V}$ ব্যাটারির সাথে সংযুক্ত করা হলো। বর্তনীর তুল্য ধারকত্ব এবং উভয় ধারকে সঞ্চিত মোট তড়িৎ শক্তি কত?</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##
+একটি ধারককে ব্যাটারির সাথে যুক্ত রেখে এর পাতদ্বয়ের মাঝে $K = 3.0$ ডাই-ইলেকট্রিক প্রবেশ করানো হলো। ধারকত্ব, পাতদ্বয়ের বিভব, তড়িৎ ক্ষেত্র, সঞ্চিত আধান এবং স্থিতিশক্তির কী পরিবর্তন হবে?</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>$C_p = C_1 + C_2 = 8 + 8 = 16\ \mu\text{F}$।
-শক্তি $U = \frac{1}{2} C_p V^2 = 0.5 \times (16 \times 10^{-6}) \times 24^2 = 0.00461\text{ J}$।</t>
+          <t>ব্যাটারি সংযুক্ত থাকায় বিভব $V$ ধ্রুব থাকে। ক্ষেত্র $E = V/d$ ধ্রুব থাকে। ধারকত্ব $C' = K C = 3C$ (৩ গুণ)। আধান $Q' = C' V = 3Q$ (৩ গুণ)। সঞ্চিত শক্তি $U' = \frac{1}{2} C' V^2 = 3U$ (৩ গুণ বৃদ্ধি পায়)।</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>$C_p = 16\ \mu\text{F}, U = 0.00461\text{ J}$</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
+          <t>বিভব ও ক্ষেত্র অপরিবর্তিত, কিন্তু ধারকত্ব, আধান ও শক্তি $3.0$ গুণ বৃদ্ধি পাবে</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6063,38 +5766,38 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>ধারকত্ব, সঞ্চিত শক্তি ও সমান্তরাল পাত ধারক 47</t>
+          <t>উন্নত স্থির তড়িৎ বিশ্লেষণ ও সমস্যাবলি (Advanced Electrostatics Synthesis)</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>$9\ \mu\text{F}$ এবং $9\ \mu\text{F}$ ধারকত্বের দুটি ধারককে সমান্তরালে যুক্ত করে $26\text{ V}$ ব্যাটারির সাথে সংযুক্ত করা হলো। বর্তনীর তুল্য ধারকত্ব এবং উভয় ধারকে সঞ্চিত মোট তড়িৎ শক্তি কত?</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr"/>
+          <t>##GEO:circle[r=3][size:small]##
+দুটি সমকেন্দ্রিক পরিবাহী গোলকের ব্যাসার্ধ $R_1$ এবং $R_2$ ($R_1 &lt; R_2$)। উভয়ের মধ্যবর্তী স্থানে আপেক্ষিক প্রবেশ্যতা $\epsilon_r$ বিশিষ্ট মাধ্যম পূর্ণ থাকলে ব্যবস্থাটির ধারকত্ব প্রতিপাদন কর।</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>$C_p = C_1 + C_2 = 9 + 9 = 18\ \mu\text{F}$।
-শক্তি $U = \frac{1}{2} C_p V^2 = 0.5 \times (18 \times 10^{-6}) \times 26^2 = 0.00608\text{ J}$।</t>
+          <t>গোলকদ্বয়ের মধ্যে প্রাবল্য $E(r) = \frac{Q}{4\pi\epsilon_0\epsilon_r r^2}$। বিভব পার্থক্য $V = \int_{R_1}^{R_2} E dr = \frac{Q}{4\pi\epsilon_0\epsilon_r}\left(\frac{1}{R_1} - \frac{1}{R_2}\right) = \frac{Q(R_2 - R_1)}{4\pi\epsilon_0\epsilon_r R_1 R_2}$। অতএব $C = \frac{Q}{V} = 4\pi\epsilon_0\epsilon_r \frac{R_1 R_2}{R_2 - R_1}$।</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>$C_p = 18\ \mu\text{F}, U = 0.00608\text{ J}$</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
+          <t>$C = 4\pi\epsilon_0 \epsilon_r \frac{R_1 R_2}{R_2 - R_1}$</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6114,43 +5817,38 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>ধারকত্ব, সঞ্চিত শক্তি ও সমান্তরাল পাত ধারক 48</t>
+          <t>উন্নত স্থির তড়িৎ বিশ্লেষণ ও সমস্যাবলি (Advanced Electrostatics Synthesis)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>##PRESET:circuit-resistors[size:medium]##
-$2\ \mu\text{F}$ এবং $4\ \mu\text{F}$ ধারকত্বের দুটি ধারককে সমান্তরালে যুক্ত করে $28\text{ V}$ ব্যাটারির সাথে সংযুক্ত করা হলো। বর্তনীর তুল্য ধারকত্ব এবং উভয় ধারকে সঞ্চিত মোট তড়িৎ শক্তি কত?</t>
+          <t>##GEO:rect[w=3,h=3][size:small]##
+একটি ঘনকের ৮টি কোণায় ৮টি সমান আধান $q$ স্থাপিত। ঘনকের কেন্দ্রবিন্দুতে তড়িৎ প্রাবল্য এবং তড়িৎ বিভবের মান কত? (প্রতি বাহু $a$)।</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>##PRESET:circuit-resistors[size:medium]##</t>
+          <t>##GEO:rect[w=3,h=3][size:small]##</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>$C_p = C_1 + C_2 = 2 + 4 = 6\ \mu\text{F}$।
-শক্তি $U = \frac{1}{2} C_p V^2 = 0.5 \times (6 \times 10^{-6}) \times 28^2 = 0.00235\text{ J}$।</t>
+          <t>প্রতিসাম্যের কারণে বিপরীত কোণার সমান আধানগুলোর প্রাবল্য পরস্পরকে নাকচ করায় কেন্দ্রে লব্ধি প্রাবল্য শূন্য: $E = 0$। কিন্তু বিভব স্কেলার রাশি হওয়ায় যোগ হবে: কোণা হতে কেন্দ্রের দূরত্ব $r = \frac{\sqrt{3}}{2}a$। মোট বিভব $V = 8 \times \frac{kq}{r} = 8 \frac{kq}{(\sqrt{3}/2)a} = \frac{16 kq}{\sqrt{3} a}$।</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>$C_p = 6\ \mu\text{F}, U = 0.00235\text{ J}$</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
+          <t>কেন্দ্রে প্রাবল্য $E = 0$, মোট বিভব $V = \frac{16 k q}{\sqrt{3} a}$</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6170,38 +5868,38 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>ধারকত্ব, সঞ্চিত শক্তি ও সমান্তরাল পাত ধারক 49</t>
+          <t>উন্নত স্থির তড়িৎ বিশ্লেষণ ও সমস্যাবলি (Advanced Electrostatics Synthesis)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>$3\ \mu\text{F}$ এবং $5\ \mu\text{F}$ ধারকত্বের দুটি ধারককে সমান্তরালে যুক্ত করে $30\text{ V}$ ব্যাটারির সাথে সংযুক্ত করা হলো। বর্তনীর তুল্য ধারকত্ব এবং উভয় ধারকে সঞ্চিত মোট তড়িৎ শক্তি কত?</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি সুষম তড়িৎ ক্ষেত্রে একটি ডাইপোলের সাম্যাবস্থা: কখন একটি ডাইপোল স্থায়ী সাম্যাবস্থায় (Stable equilibrium) এবং কখন অস্থায়ী সাম্যাবস্থায় (Unstable equilibrium) থাকে?</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>$C_p = C_1 + C_2 = 3 + 5 = 8\ \mu\text{F}$।
-শক্তি $U = \frac{1}{2} C_p V^2 = 0.5 \times (8 \times 10^{-6}) \times 30^2 = 0.0036\text{ J}$।</t>
+          <t>টর্ক $\tau = pE\sin\theta$। $\theta = 0^\circ$ ও $\theta = 180^\circ$ উভয়েই টর্ক শূন্য। স্থিতিশক্তি $U = -pE\cos\theta$। $\theta = 0^\circ$-তে $U = -pE$ (ন্যূনতম শক্তি), তাই সামান্য বিক্ষেপ করলে পুনরুদ্ধার টর্ক ক্রিয়া করে স্থায়ী সাম্যাবস্থায় ফিরে আসে। $\theta = 180^\circ$-তে $U = +pE$ (সর্বোচ্চ শক্তি), ফলে সামান্য বিক্ষেপেই উল্টে যায়, তাই এটি অস্থায়ী সাম্যাবস্থা।</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>$C_p = 8\ \mu\text{F}, U = 0.0036\text{ J}$</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
+          <t>$\theta = 0^\circ$-তে স্থায়ী সাম্যাবস্থা ($U = -pE$), $\theta = 180^\circ$-তে অস্থায়ী সাম্যাবস্থা ($U = +pE$)</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6221,38 +5919,38 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>ধারকত্ব, সঞ্চিত শক্তি ও সমান্তরাল পাত ধারক 50</t>
+          <t>উন্নত স্থির তড়িৎ বিশ্লেষণ ও সমস্যাবলি (Advanced Electrostatics Synthesis)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>$4\ \mu\text{F}$ এবং $6\ \mu\text{F}$ ধারকত্বের দুটি ধারককে সমান্তরালে যুক্ত করে $12\text{ V}$ ব্যাটারির সাথে সংযুক্ত করা হলো। বর্তনীর তুল্য ধারকত্ব এবং উভয় ধারকে সঞ্চিত মোট তড়িৎ শক্তি কত?</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+স্থির তড়িতে আর্নিং বা ভূ-সংযুক্তকরণের তাৎপর্য: কোনো আহিত পরিবাহীকে পৃথিবীর সাথে তার দ্বারা যুক্ত করলে পরিবাহীর সমস্ত আধান কেন মাটিতে চলে যায়?</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>$C_p = C_1 + C_2 = 4 + 6 = 10\ \mu\text{F}$।
-শক্তি $U = \frac{1}{2} C_p V^2 = 0.5 \times (10 \times 10^{-6}) \times 12^2 = 0.00072\text{ J}$।</t>
+          <t>পৃথিবীর ব্যাসার্ধ $R \approx 6.4 \times 10^6\text{ m}$ অত্যন্ত বিশাল হওয়ায় এর ধারকত্ব $C = 4\pi\epsilon_0 R \approx 711\text{ }\mu\text{F}$ বিশাল। পরিবাহীকে ভূ-সংযুক্ত করলে আধানের প্রবাহ ততক্ষণ চলে যতক্ষণ না পরিবাহীর বিভব পৃথিবীর বিভবের (শূন্য ভোল্ট) সমান হয়।</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>$C_p = 10\ \mu\text{F}, U = 0.00072\text{ J}$</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
+          <t>পৃথিবীর বিশাল ধারকত্বের কারণে এর বিভব শূন্য ধরা হয়; উচ্চ বা নিম্ন বিভবের পরিবাহী ভূমির শূন্য বিভবে সমতায় আসে</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
